--- a/images_master.xlsx
+++ b/images_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fengbo/GitHub/soseki-manuscripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D2AB1D-F107-5B43-8044-0968743D5A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F6019F-E7FC-E847-8C7A-E53354F66548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16820" yWindow="620" windowWidth="15180" windowHeight="16160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="288">
   <si>
     <t>image_id</t>
   </si>
@@ -899,6 +899,10 @@
   </si>
   <si>
     <t>当前状态</t>
+  </si>
+  <si>
+    <t>w02</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1233,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q248"/>
+  <dimension ref="A1:Q249"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -8090,7 +8094,7 @@
     </row>
     <row r="130" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="7" t="str">
-        <f t="shared" ref="A130:A193" si="16">IF(OR(B130="",D130=""),"",B130&amp;IF(C130="","","-"&amp;C130)&amp;"-p"&amp;D130)</f>
+        <f t="shared" ref="A130:A194" si="16">IF(OR(B130="",D130=""),"",B130&amp;IF(C130="","","-"&amp;C130)&amp;"-p"&amp;D130)</f>
         <v>128-w01-p1</v>
       </c>
       <c r="B130" s="8" t="s">
@@ -8106,34 +8110,34 @@
         <v>19</v>
       </c>
       <c r="F130" s="8" t="str">
-        <f t="shared" ref="F130:F193" si="17">IF(OR(B130="",C130=""),"",B130&amp;"-"&amp;C130&amp;".jpg")</f>
+        <f t="shared" ref="F130:F194" si="17">IF(OR(B130="",C130=""),"",B130&amp;"-"&amp;C130&amp;".jpg")</f>
         <v>128-w01.jpg</v>
       </c>
       <c r="G130" s="8" t="str">
-        <f t="shared" ref="G130:G193" si="18">IF(OR(B130="",C130=""),"","images/"&amp;B130&amp;"-"&amp;C130&amp;".jpg")</f>
+        <f t="shared" ref="G130:G194" si="18">IF(OR(B130="",C130=""),"","images/"&amp;B130&amp;"-"&amp;C130&amp;".jpg")</f>
         <v>images/128-w01.jpg</v>
       </c>
       <c r="H130" s="8" t="str">
-        <f t="shared" ref="H130:H193" si="19">IF(OR(B130="",C130=""),"","https://scholarbo.github.io/soseki-manuscripts/images/"&amp;B130&amp;"-"&amp;C130&amp;".jpg")</f>
+        <f t="shared" ref="H130:H194" si="19">IF(OR(B130="",C130=""),"","https://scholarbo.github.io/soseki-manuscripts/images/"&amp;B130&amp;"-"&amp;C130&amp;".jpg")</f>
         <v>https://scholarbo.github.io/soseki-manuscripts/images/128-w01.jpg</v>
       </c>
       <c r="I130" s="8"/>
       <c r="J130" s="8" t="str">
-        <f t="shared" ref="J130:J193" si="20">IF(OR(B130="",C130="",E130&lt;&gt;"iiif"),"","images/"&amp;B130&amp;"-"&amp;C130&amp;".jpg")</f>
+        <f t="shared" ref="J130:J194" si="20">IF(OR(B130="",C130="",E130&lt;&gt;"iiif"),"","images/"&amp;B130&amp;"-"&amp;C130&amp;".jpg")</f>
         <v>images/128-w01.jpg</v>
       </c>
       <c r="K130" s="8"/>
       <c r="L130" s="8"/>
       <c r="M130" s="7" t="str">
-        <f t="shared" ref="M130:M193" si="21">IF(OR(B130="",D130=""),"",B130&amp;IF(C130="","",IF(C130="w01",""," 第"&amp;VALUE(RIGHT(C130,2))&amp;"版"))&amp;" 第"&amp;D130&amp;"頁")</f>
+        <f t="shared" ref="M130:M194" si="21">IF(OR(B130="",D130=""),"",B130&amp;IF(C130="","",IF(C130="w01",""," 第"&amp;VALUE(RIGHT(C130,2))&amp;"版"))&amp;" 第"&amp;D130&amp;"頁")</f>
         <v>128 第1頁</v>
       </c>
       <c r="N130" s="7" t="str">
-        <f t="shared" ref="N130:N193" si="22">IF(OR(B130="",C130=""),"","manifest-"&amp;B130&amp;"-"&amp;C130)</f>
+        <f t="shared" ref="N130:N194" si="22">IF(OR(B130="",C130=""),"","manifest-"&amp;B130&amp;"-"&amp;C130)</f>
         <v>manifest-128-w01</v>
       </c>
       <c r="O130" s="7" t="str">
-        <f t="shared" ref="O130:O193" si="23">IF(OR(B130="",C130="",D130=""),"","canvas-"&amp;B130&amp;"-"&amp;C130&amp;IF(D130=1,"","-p"&amp;D130))</f>
+        <f t="shared" ref="O130:O194" si="23">IF(OR(B130="",C130="",D130=""),"","canvas-"&amp;B130&amp;"-"&amp;C130&amp;IF(D130=1,"","-p"&amp;D130))</f>
         <v>canvas-128-w01</v>
       </c>
       <c r="P130" s="8" t="s">
@@ -8461,14 +8465,14 @@
     </row>
     <row r="137" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="7" t="str">
-        <f t="shared" si="16"/>
-        <v>135-w01-p1</v>
+        <f t="shared" ref="A137" si="24">IF(OR(B137="",D137=""),"",B137&amp;IF(C137="","","-"&amp;C137)&amp;"-p"&amp;D137)</f>
+        <v>134-w02-p1</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>18</v>
+        <v>287</v>
       </c>
       <c r="D137" s="8">
         <v>1</v>
@@ -8477,35 +8481,35 @@
         <v>19</v>
       </c>
       <c r="F137" s="8" t="str">
-        <f t="shared" si="17"/>
-        <v>135-w01.jpg</v>
+        <f t="shared" ref="F137" si="25">IF(OR(B137="",C137=""),"",B137&amp;"-"&amp;C137&amp;".jpg")</f>
+        <v>134-w02.jpg</v>
       </c>
       <c r="G137" s="8" t="str">
-        <f t="shared" si="18"/>
-        <v>images/135-w01.jpg</v>
+        <f t="shared" ref="G137" si="26">IF(OR(B137="",C137=""),"","images/"&amp;B137&amp;"-"&amp;C137&amp;".jpg")</f>
+        <v>images/134-w02.jpg</v>
       </c>
       <c r="H137" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/135-w01.jpg</v>
+        <f t="shared" ref="H137" si="27">IF(OR(B137="",C137=""),"","https://scholarbo.github.io/soseki-manuscripts/images/"&amp;B137&amp;"-"&amp;C137&amp;".jpg")</f>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/134-w02.jpg</v>
       </c>
       <c r="I137" s="8"/>
       <c r="J137" s="8" t="str">
-        <f t="shared" si="20"/>
-        <v>images/135-w01.jpg</v>
+        <f t="shared" ref="J137" si="28">IF(OR(B137="",C137="",E137&lt;&gt;"iiif"),"","images/"&amp;B137&amp;"-"&amp;C137&amp;".jpg")</f>
+        <v>images/134-w02.jpg</v>
       </c>
       <c r="K137" s="8"/>
       <c r="L137" s="8"/>
       <c r="M137" s="7" t="str">
-        <f t="shared" si="21"/>
-        <v>135 第1頁</v>
+        <f t="shared" ref="M137" si="29">IF(OR(B137="",D137=""),"",B137&amp;IF(C137="","",IF(C137="w01",""," 第"&amp;VALUE(RIGHT(C137,2))&amp;"版"))&amp;" 第"&amp;D137&amp;"頁")</f>
+        <v>134 第2版 第1頁</v>
       </c>
       <c r="N137" s="7" t="str">
-        <f t="shared" si="22"/>
-        <v>manifest-135-w01</v>
+        <f t="shared" ref="N137" si="30">IF(OR(B137="",C137=""),"","manifest-"&amp;B137&amp;"-"&amp;C137)</f>
+        <v>manifest-134-w02</v>
       </c>
       <c r="O137" s="7" t="str">
-        <f t="shared" si="23"/>
-        <v>canvas-135-w01</v>
+        <f t="shared" ref="O137" si="31">IF(OR(B137="",C137="",D137=""),"","canvas-"&amp;B137&amp;"-"&amp;C137&amp;IF(D137=1,"","-p"&amp;D137))</f>
+        <v>canvas-134-w02</v>
       </c>
       <c r="P137" s="8" t="s">
         <v>20</v>
@@ -8515,10 +8519,10 @@
     <row r="138" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>136-w01-p1</v>
+        <v>135-w01-p1</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>18</v>
@@ -8531,34 +8535,34 @@
       </c>
       <c r="F138" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>136-w01.jpg</v>
+        <v>135-w01.jpg</v>
       </c>
       <c r="G138" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/136-w01.jpg</v>
+        <v>images/135-w01.jpg</v>
       </c>
       <c r="H138" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/136-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/135-w01.jpg</v>
       </c>
       <c r="I138" s="8"/>
       <c r="J138" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/136-w01.jpg</v>
+        <v>images/135-w01.jpg</v>
       </c>
       <c r="K138" s="8"/>
       <c r="L138" s="8"/>
       <c r="M138" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>136 第1頁</v>
+        <v>135 第1頁</v>
       </c>
       <c r="N138" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-136-w01</v>
+        <v>manifest-135-w01</v>
       </c>
       <c r="O138" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-136-w01</v>
+        <v>canvas-135-w01</v>
       </c>
       <c r="P138" s="8" t="s">
         <v>20</v>
@@ -8568,10 +8572,10 @@
     <row r="139" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>137-w01-p1</v>
+        <v>136-w01-p1</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>18</v>
@@ -8584,34 +8588,34 @@
       </c>
       <c r="F139" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>137-w01.jpg</v>
+        <v>136-w01.jpg</v>
       </c>
       <c r="G139" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/137-w01.jpg</v>
+        <v>images/136-w01.jpg</v>
       </c>
       <c r="H139" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/137-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/136-w01.jpg</v>
       </c>
       <c r="I139" s="8"/>
       <c r="J139" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/137-w01.jpg</v>
+        <v>images/136-w01.jpg</v>
       </c>
       <c r="K139" s="8"/>
       <c r="L139" s="8"/>
       <c r="M139" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>137 第1頁</v>
+        <v>136 第1頁</v>
       </c>
       <c r="N139" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-137-w01</v>
+        <v>manifest-136-w01</v>
       </c>
       <c r="O139" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-137-w01</v>
+        <v>canvas-136-w01</v>
       </c>
       <c r="P139" s="8" t="s">
         <v>20</v>
@@ -8621,10 +8625,10 @@
     <row r="140" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>138-w01-p1</v>
+        <v>137-w01-p1</v>
       </c>
       <c r="B140" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>18</v>
@@ -8637,34 +8641,34 @@
       </c>
       <c r="F140" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>138-w01.jpg</v>
+        <v>137-w01.jpg</v>
       </c>
       <c r="G140" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/138-w01.jpg</v>
+        <v>images/137-w01.jpg</v>
       </c>
       <c r="H140" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/138-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/137-w01.jpg</v>
       </c>
       <c r="I140" s="8"/>
       <c r="J140" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/138-w01.jpg</v>
+        <v>images/137-w01.jpg</v>
       </c>
       <c r="K140" s="8"/>
       <c r="L140" s="8"/>
       <c r="M140" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>138 第1頁</v>
+        <v>137 第1頁</v>
       </c>
       <c r="N140" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-138-w01</v>
+        <v>manifest-137-w01</v>
       </c>
       <c r="O140" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-138-w01</v>
+        <v>canvas-137-w01</v>
       </c>
       <c r="P140" s="8" t="s">
         <v>20</v>
@@ -8674,10 +8678,10 @@
     <row r="141" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>139-w01-p1</v>
+        <v>138-w01-p1</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>18</v>
@@ -8690,34 +8694,34 @@
       </c>
       <c r="F141" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>139-w01.jpg</v>
+        <v>138-w01.jpg</v>
       </c>
       <c r="G141" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/139-w01.jpg</v>
+        <v>images/138-w01.jpg</v>
       </c>
       <c r="H141" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/139-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/138-w01.jpg</v>
       </c>
       <c r="I141" s="8"/>
       <c r="J141" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/139-w01.jpg</v>
+        <v>images/138-w01.jpg</v>
       </c>
       <c r="K141" s="8"/>
       <c r="L141" s="8"/>
       <c r="M141" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>139 第1頁</v>
+        <v>138 第1頁</v>
       </c>
       <c r="N141" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-139-w01</v>
+        <v>manifest-138-w01</v>
       </c>
       <c r="O141" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-139-w01</v>
+        <v>canvas-138-w01</v>
       </c>
       <c r="P141" s="8" t="s">
         <v>20</v>
@@ -8727,10 +8731,10 @@
     <row r="142" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>140-w01-p1</v>
+        <v>139-w01-p1</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>18</v>
@@ -8743,34 +8747,34 @@
       </c>
       <c r="F142" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>140-w01.jpg</v>
+        <v>139-w01.jpg</v>
       </c>
       <c r="G142" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/140-w01.jpg</v>
+        <v>images/139-w01.jpg</v>
       </c>
       <c r="H142" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/140-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/139-w01.jpg</v>
       </c>
       <c r="I142" s="8"/>
       <c r="J142" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/140-w01.jpg</v>
+        <v>images/139-w01.jpg</v>
       </c>
       <c r="K142" s="8"/>
       <c r="L142" s="8"/>
       <c r="M142" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>140 第1頁</v>
+        <v>139 第1頁</v>
       </c>
       <c r="N142" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-140-w01</v>
+        <v>manifest-139-w01</v>
       </c>
       <c r="O142" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-140-w01</v>
+        <v>canvas-139-w01</v>
       </c>
       <c r="P142" s="8" t="s">
         <v>20</v>
@@ -8780,10 +8784,10 @@
     <row r="143" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>141-w01-p1</v>
+        <v>140-w01-p1</v>
       </c>
       <c r="B143" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>18</v>
@@ -8796,34 +8800,34 @@
       </c>
       <c r="F143" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>141-w01.jpg</v>
+        <v>140-w01.jpg</v>
       </c>
       <c r="G143" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/141-w01.jpg</v>
+        <v>images/140-w01.jpg</v>
       </c>
       <c r="H143" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/141-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/140-w01.jpg</v>
       </c>
       <c r="I143" s="8"/>
       <c r="J143" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/141-w01.jpg</v>
+        <v>images/140-w01.jpg</v>
       </c>
       <c r="K143" s="8"/>
       <c r="L143" s="8"/>
       <c r="M143" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>141 第1頁</v>
+        <v>140 第1頁</v>
       </c>
       <c r="N143" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-141-w01</v>
+        <v>manifest-140-w01</v>
       </c>
       <c r="O143" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-141-w01</v>
+        <v>canvas-140-w01</v>
       </c>
       <c r="P143" s="8" t="s">
         <v>20</v>
@@ -8833,10 +8837,10 @@
     <row r="144" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>142-w01-p1</v>
+        <v>141-w01-p1</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>18</v>
@@ -8849,34 +8853,34 @@
       </c>
       <c r="F144" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>142-w01.jpg</v>
+        <v>141-w01.jpg</v>
       </c>
       <c r="G144" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/142-w01.jpg</v>
+        <v>images/141-w01.jpg</v>
       </c>
       <c r="H144" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/142-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/141-w01.jpg</v>
       </c>
       <c r="I144" s="8"/>
       <c r="J144" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/142-w01.jpg</v>
+        <v>images/141-w01.jpg</v>
       </c>
       <c r="K144" s="8"/>
       <c r="L144" s="8"/>
       <c r="M144" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>142 第1頁</v>
+        <v>141 第1頁</v>
       </c>
       <c r="N144" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-142-w01</v>
+        <v>manifest-141-w01</v>
       </c>
       <c r="O144" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-142-w01</v>
+        <v>canvas-141-w01</v>
       </c>
       <c r="P144" s="8" t="s">
         <v>20</v>
@@ -8886,10 +8890,10 @@
     <row r="145" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>143-w01-p1</v>
+        <v>142-w01-p1</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>18</v>
@@ -8902,34 +8906,34 @@
       </c>
       <c r="F145" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>143-w01.jpg</v>
+        <v>142-w01.jpg</v>
       </c>
       <c r="G145" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/143-w01.jpg</v>
+        <v>images/142-w01.jpg</v>
       </c>
       <c r="H145" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/143-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/142-w01.jpg</v>
       </c>
       <c r="I145" s="8"/>
       <c r="J145" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/143-w01.jpg</v>
+        <v>images/142-w01.jpg</v>
       </c>
       <c r="K145" s="8"/>
       <c r="L145" s="8"/>
       <c r="M145" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>143 第1頁</v>
+        <v>142 第1頁</v>
       </c>
       <c r="N145" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-143-w01</v>
+        <v>manifest-142-w01</v>
       </c>
       <c r="O145" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-143-w01</v>
+        <v>canvas-142-w01</v>
       </c>
       <c r="P145" s="8" t="s">
         <v>20</v>
@@ -8939,10 +8943,10 @@
     <row r="146" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>144-w01-p1</v>
+        <v>143-w01-p1</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>18</v>
@@ -8955,34 +8959,34 @@
       </c>
       <c r="F146" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>144-w01.jpg</v>
+        <v>143-w01.jpg</v>
       </c>
       <c r="G146" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/144-w01.jpg</v>
+        <v>images/143-w01.jpg</v>
       </c>
       <c r="H146" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/144-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/143-w01.jpg</v>
       </c>
       <c r="I146" s="8"/>
       <c r="J146" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/144-w01.jpg</v>
+        <v>images/143-w01.jpg</v>
       </c>
       <c r="K146" s="8"/>
       <c r="L146" s="8"/>
       <c r="M146" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>144 第1頁</v>
+        <v>143 第1頁</v>
       </c>
       <c r="N146" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-144-w01</v>
+        <v>manifest-143-w01</v>
       </c>
       <c r="O146" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-144-w01</v>
+        <v>canvas-143-w01</v>
       </c>
       <c r="P146" s="8" t="s">
         <v>20</v>
@@ -8992,10 +8996,10 @@
     <row r="147" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>145-w01-p1</v>
+        <v>144-w01-p1</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>18</v>
@@ -9008,34 +9012,34 @@
       </c>
       <c r="F147" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>145-w01.jpg</v>
+        <v>144-w01.jpg</v>
       </c>
       <c r="G147" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/145-w01.jpg</v>
+        <v>images/144-w01.jpg</v>
       </c>
       <c r="H147" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/145-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/144-w01.jpg</v>
       </c>
       <c r="I147" s="8"/>
       <c r="J147" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/145-w01.jpg</v>
+        <v>images/144-w01.jpg</v>
       </c>
       <c r="K147" s="8"/>
       <c r="L147" s="8"/>
       <c r="M147" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>145 第1頁</v>
+        <v>144 第1頁</v>
       </c>
       <c r="N147" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-145-w01</v>
+        <v>manifest-144-w01</v>
       </c>
       <c r="O147" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-145-w01</v>
+        <v>canvas-144-w01</v>
       </c>
       <c r="P147" s="8" t="s">
         <v>20</v>
@@ -9045,10 +9049,10 @@
     <row r="148" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>146-w01-p1</v>
+        <v>145-w01-p1</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>18</v>
@@ -9061,34 +9065,34 @@
       </c>
       <c r="F148" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>146-w01.jpg</v>
+        <v>145-w01.jpg</v>
       </c>
       <c r="G148" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/146-w01.jpg</v>
+        <v>images/145-w01.jpg</v>
       </c>
       <c r="H148" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/146-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/145-w01.jpg</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/146-w01.jpg</v>
+        <v>images/145-w01.jpg</v>
       </c>
       <c r="K148" s="8"/>
       <c r="L148" s="8"/>
       <c r="M148" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>146 第1頁</v>
+        <v>145 第1頁</v>
       </c>
       <c r="N148" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-146-w01</v>
+        <v>manifest-145-w01</v>
       </c>
       <c r="O148" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-146-w01</v>
+        <v>canvas-145-w01</v>
       </c>
       <c r="P148" s="8" t="s">
         <v>20</v>
@@ -9098,10 +9102,10 @@
     <row r="149" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>147-w01-p1</v>
+        <v>146-w01-p1</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>18</v>
@@ -9114,34 +9118,34 @@
       </c>
       <c r="F149" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>147-w01.jpg</v>
+        <v>146-w01.jpg</v>
       </c>
       <c r="G149" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/147-w01.jpg</v>
+        <v>images/146-w01.jpg</v>
       </c>
       <c r="H149" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/147-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/146-w01.jpg</v>
       </c>
       <c r="I149" s="8"/>
       <c r="J149" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/147-w01.jpg</v>
+        <v>images/146-w01.jpg</v>
       </c>
       <c r="K149" s="8"/>
       <c r="L149" s="8"/>
       <c r="M149" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>147 第1頁</v>
+        <v>146 第1頁</v>
       </c>
       <c r="N149" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-147-w01</v>
+        <v>manifest-146-w01</v>
       </c>
       <c r="O149" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-147-w01</v>
+        <v>canvas-146-w01</v>
       </c>
       <c r="P149" s="8" t="s">
         <v>20</v>
@@ -9151,10 +9155,10 @@
     <row r="150" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>148-w01-p1</v>
+        <v>147-w01-p1</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>18</v>
@@ -9167,34 +9171,34 @@
       </c>
       <c r="F150" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>148-w01.jpg</v>
+        <v>147-w01.jpg</v>
       </c>
       <c r="G150" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/148-w01.jpg</v>
+        <v>images/147-w01.jpg</v>
       </c>
       <c r="H150" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/148-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/147-w01.jpg</v>
       </c>
       <c r="I150" s="8"/>
       <c r="J150" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/148-w01.jpg</v>
+        <v>images/147-w01.jpg</v>
       </c>
       <c r="K150" s="8"/>
       <c r="L150" s="8"/>
       <c r="M150" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>148 第1頁</v>
+        <v>147 第1頁</v>
       </c>
       <c r="N150" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-148-w01</v>
+        <v>manifest-147-w01</v>
       </c>
       <c r="O150" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-148-w01</v>
+        <v>canvas-147-w01</v>
       </c>
       <c r="P150" s="8" t="s">
         <v>20</v>
@@ -9204,10 +9208,10 @@
     <row r="151" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>149-w01-p1</v>
+        <v>148-w01-p1</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>18</v>
@@ -9220,34 +9224,34 @@
       </c>
       <c r="F151" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>149-w01.jpg</v>
+        <v>148-w01.jpg</v>
       </c>
       <c r="G151" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/149-w01.jpg</v>
+        <v>images/148-w01.jpg</v>
       </c>
       <c r="H151" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/149-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/148-w01.jpg</v>
       </c>
       <c r="I151" s="8"/>
       <c r="J151" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/149-w01.jpg</v>
+        <v>images/148-w01.jpg</v>
       </c>
       <c r="K151" s="8"/>
       <c r="L151" s="8"/>
       <c r="M151" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>149 第1頁</v>
+        <v>148 第1頁</v>
       </c>
       <c r="N151" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-149-w01</v>
+        <v>manifest-148-w01</v>
       </c>
       <c r="O151" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-149-w01</v>
+        <v>canvas-148-w01</v>
       </c>
       <c r="P151" s="8" t="s">
         <v>20</v>
@@ -9257,10 +9261,10 @@
     <row r="152" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>150-w01-p1</v>
+        <v>149-w01-p1</v>
       </c>
       <c r="B152" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>18</v>
@@ -9273,34 +9277,34 @@
       </c>
       <c r="F152" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>150-w01.jpg</v>
+        <v>149-w01.jpg</v>
       </c>
       <c r="G152" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/150-w01.jpg</v>
+        <v>images/149-w01.jpg</v>
       </c>
       <c r="H152" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/150-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/149-w01.jpg</v>
       </c>
       <c r="I152" s="8"/>
       <c r="J152" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/150-w01.jpg</v>
+        <v>images/149-w01.jpg</v>
       </c>
       <c r="K152" s="8"/>
       <c r="L152" s="8"/>
       <c r="M152" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>150 第1頁</v>
+        <v>149 第1頁</v>
       </c>
       <c r="N152" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-150-w01</v>
+        <v>manifest-149-w01</v>
       </c>
       <c r="O152" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-150-w01</v>
+        <v>canvas-149-w01</v>
       </c>
       <c r="P152" s="8" t="s">
         <v>20</v>
@@ -9310,10 +9314,10 @@
     <row r="153" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>151-w01-p1</v>
+        <v>150-w01-p1</v>
       </c>
       <c r="B153" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>18</v>
@@ -9326,34 +9330,34 @@
       </c>
       <c r="F153" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>151-w01.jpg</v>
+        <v>150-w01.jpg</v>
       </c>
       <c r="G153" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/151-w01.jpg</v>
+        <v>images/150-w01.jpg</v>
       </c>
       <c r="H153" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/151-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/150-w01.jpg</v>
       </c>
       <c r="I153" s="8"/>
       <c r="J153" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/151-w01.jpg</v>
+        <v>images/150-w01.jpg</v>
       </c>
       <c r="K153" s="8"/>
       <c r="L153" s="8"/>
       <c r="M153" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>151 第1頁</v>
+        <v>150 第1頁</v>
       </c>
       <c r="N153" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-151-w01</v>
+        <v>manifest-150-w01</v>
       </c>
       <c r="O153" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-151-w01</v>
+        <v>canvas-150-w01</v>
       </c>
       <c r="P153" s="8" t="s">
         <v>20</v>
@@ -9363,10 +9367,10 @@
     <row r="154" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>152-w01-p1</v>
+        <v>151-w01-p1</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>18</v>
@@ -9379,34 +9383,34 @@
       </c>
       <c r="F154" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>152-w01.jpg</v>
+        <v>151-w01.jpg</v>
       </c>
       <c r="G154" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/152-w01.jpg</v>
+        <v>images/151-w01.jpg</v>
       </c>
       <c r="H154" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/152-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/151-w01.jpg</v>
       </c>
       <c r="I154" s="8"/>
       <c r="J154" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/152-w01.jpg</v>
+        <v>images/151-w01.jpg</v>
       </c>
       <c r="K154" s="8"/>
       <c r="L154" s="8"/>
       <c r="M154" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>152 第1頁</v>
+        <v>151 第1頁</v>
       </c>
       <c r="N154" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-152-w01</v>
+        <v>manifest-151-w01</v>
       </c>
       <c r="O154" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-152-w01</v>
+        <v>canvas-151-w01</v>
       </c>
       <c r="P154" s="8" t="s">
         <v>20</v>
@@ -9416,10 +9420,10 @@
     <row r="155" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>153-w01-p1</v>
+        <v>152-w01-p1</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>18</v>
@@ -9432,34 +9436,34 @@
       </c>
       <c r="F155" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>153-w01.jpg</v>
+        <v>152-w01.jpg</v>
       </c>
       <c r="G155" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/153-w01.jpg</v>
+        <v>images/152-w01.jpg</v>
       </c>
       <c r="H155" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/153-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/152-w01.jpg</v>
       </c>
       <c r="I155" s="8"/>
       <c r="J155" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/153-w01.jpg</v>
+        <v>images/152-w01.jpg</v>
       </c>
       <c r="K155" s="8"/>
       <c r="L155" s="8"/>
       <c r="M155" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>153 第1頁</v>
+        <v>152 第1頁</v>
       </c>
       <c r="N155" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-153-w01</v>
+        <v>manifest-152-w01</v>
       </c>
       <c r="O155" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-153-w01</v>
+        <v>canvas-152-w01</v>
       </c>
       <c r="P155" s="8" t="s">
         <v>20</v>
@@ -9469,10 +9473,10 @@
     <row r="156" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>154-w01-p1</v>
+        <v>153-w01-p1</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>18</v>
@@ -9485,34 +9489,34 @@
       </c>
       <c r="F156" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>154-w01.jpg</v>
+        <v>153-w01.jpg</v>
       </c>
       <c r="G156" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/154-w01.jpg</v>
+        <v>images/153-w01.jpg</v>
       </c>
       <c r="H156" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/154-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/153-w01.jpg</v>
       </c>
       <c r="I156" s="8"/>
       <c r="J156" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/154-w01.jpg</v>
+        <v>images/153-w01.jpg</v>
       </c>
       <c r="K156" s="8"/>
       <c r="L156" s="8"/>
       <c r="M156" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>154 第1頁</v>
+        <v>153 第1頁</v>
       </c>
       <c r="N156" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-154-w01</v>
+        <v>manifest-153-w01</v>
       </c>
       <c r="O156" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-154-w01</v>
+        <v>canvas-153-w01</v>
       </c>
       <c r="P156" s="8" t="s">
         <v>20</v>
@@ -9522,10 +9526,10 @@
     <row r="157" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>155-w01-p1</v>
+        <v>154-w01-p1</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>18</v>
@@ -9538,34 +9542,34 @@
       </c>
       <c r="F157" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>155-w01.jpg</v>
+        <v>154-w01.jpg</v>
       </c>
       <c r="G157" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/155-w01.jpg</v>
+        <v>images/154-w01.jpg</v>
       </c>
       <c r="H157" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/155-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/154-w01.jpg</v>
       </c>
       <c r="I157" s="8"/>
       <c r="J157" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/155-w01.jpg</v>
+        <v>images/154-w01.jpg</v>
       </c>
       <c r="K157" s="8"/>
       <c r="L157" s="8"/>
       <c r="M157" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>155 第1頁</v>
+        <v>154 第1頁</v>
       </c>
       <c r="N157" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-155-w01</v>
+        <v>manifest-154-w01</v>
       </c>
       <c r="O157" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-155-w01</v>
+        <v>canvas-154-w01</v>
       </c>
       <c r="P157" s="8" t="s">
         <v>20</v>
@@ -9575,10 +9579,10 @@
     <row r="158" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>156-w01-p1</v>
+        <v>155-w01-p1</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>18</v>
@@ -9591,34 +9595,34 @@
       </c>
       <c r="F158" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>156-w01.jpg</v>
+        <v>155-w01.jpg</v>
       </c>
       <c r="G158" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/156-w01.jpg</v>
+        <v>images/155-w01.jpg</v>
       </c>
       <c r="H158" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/156-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/155-w01.jpg</v>
       </c>
       <c r="I158" s="8"/>
       <c r="J158" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/156-w01.jpg</v>
+        <v>images/155-w01.jpg</v>
       </c>
       <c r="K158" s="8"/>
       <c r="L158" s="8"/>
       <c r="M158" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>156 第1頁</v>
+        <v>155 第1頁</v>
       </c>
       <c r="N158" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-156-w01</v>
+        <v>manifest-155-w01</v>
       </c>
       <c r="O158" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-156-w01</v>
+        <v>canvas-155-w01</v>
       </c>
       <c r="P158" s="8" t="s">
         <v>20</v>
@@ -9628,10 +9632,10 @@
     <row r="159" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>157-w01-p1</v>
+        <v>156-w01-p1</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>18</v>
@@ -9644,34 +9648,34 @@
       </c>
       <c r="F159" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>157-w01.jpg</v>
+        <v>156-w01.jpg</v>
       </c>
       <c r="G159" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/157-w01.jpg</v>
+        <v>images/156-w01.jpg</v>
       </c>
       <c r="H159" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/157-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/156-w01.jpg</v>
       </c>
       <c r="I159" s="8"/>
       <c r="J159" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/157-w01.jpg</v>
+        <v>images/156-w01.jpg</v>
       </c>
       <c r="K159" s="8"/>
       <c r="L159" s="8"/>
       <c r="M159" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>157 第1頁</v>
+        <v>156 第1頁</v>
       </c>
       <c r="N159" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-157-w01</v>
+        <v>manifest-156-w01</v>
       </c>
       <c r="O159" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-157-w01</v>
+        <v>canvas-156-w01</v>
       </c>
       <c r="P159" s="8" t="s">
         <v>20</v>
@@ -9681,10 +9685,10 @@
     <row r="160" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>158-w01-p1</v>
+        <v>157-w01-p1</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>18</v>
@@ -9697,34 +9701,34 @@
       </c>
       <c r="F160" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>158-w01.jpg</v>
+        <v>157-w01.jpg</v>
       </c>
       <c r="G160" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/158-w01.jpg</v>
+        <v>images/157-w01.jpg</v>
       </c>
       <c r="H160" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/158-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/157-w01.jpg</v>
       </c>
       <c r="I160" s="8"/>
       <c r="J160" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/158-w01.jpg</v>
+        <v>images/157-w01.jpg</v>
       </c>
       <c r="K160" s="8"/>
       <c r="L160" s="8"/>
       <c r="M160" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>158 第1頁</v>
+        <v>157 第1頁</v>
       </c>
       <c r="N160" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-158-w01</v>
+        <v>manifest-157-w01</v>
       </c>
       <c r="O160" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-158-w01</v>
+        <v>canvas-157-w01</v>
       </c>
       <c r="P160" s="8" t="s">
         <v>20</v>
@@ -9734,10 +9738,10 @@
     <row r="161" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>159-w01-p1</v>
+        <v>158-w01-p1</v>
       </c>
       <c r="B161" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>18</v>
@@ -9750,34 +9754,34 @@
       </c>
       <c r="F161" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>159-w01.jpg</v>
+        <v>158-w01.jpg</v>
       </c>
       <c r="G161" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/159-w01.jpg</v>
+        <v>images/158-w01.jpg</v>
       </c>
       <c r="H161" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/159-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/158-w01.jpg</v>
       </c>
       <c r="I161" s="8"/>
       <c r="J161" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/159-w01.jpg</v>
+        <v>images/158-w01.jpg</v>
       </c>
       <c r="K161" s="8"/>
       <c r="L161" s="8"/>
       <c r="M161" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>159 第1頁</v>
+        <v>158 第1頁</v>
       </c>
       <c r="N161" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-159-w01</v>
+        <v>manifest-158-w01</v>
       </c>
       <c r="O161" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-159-w01</v>
+        <v>canvas-158-w01</v>
       </c>
       <c r="P161" s="8" t="s">
         <v>20</v>
@@ -9787,10 +9791,10 @@
     <row r="162" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>160-w01-p1</v>
+        <v>159-w01-p1</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>18</v>
@@ -9803,34 +9807,34 @@
       </c>
       <c r="F162" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>160-w01.jpg</v>
+        <v>159-w01.jpg</v>
       </c>
       <c r="G162" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/160-w01.jpg</v>
+        <v>images/159-w01.jpg</v>
       </c>
       <c r="H162" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/160-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/159-w01.jpg</v>
       </c>
       <c r="I162" s="8"/>
       <c r="J162" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/160-w01.jpg</v>
+        <v>images/159-w01.jpg</v>
       </c>
       <c r="K162" s="8"/>
       <c r="L162" s="8"/>
       <c r="M162" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>160 第1頁</v>
+        <v>159 第1頁</v>
       </c>
       <c r="N162" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-160-w01</v>
+        <v>manifest-159-w01</v>
       </c>
       <c r="O162" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-160-w01</v>
+        <v>canvas-159-w01</v>
       </c>
       <c r="P162" s="8" t="s">
         <v>20</v>
@@ -9840,10 +9844,10 @@
     <row r="163" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>161-w01-p1</v>
+        <v>160-w01-p1</v>
       </c>
       <c r="B163" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>18</v>
@@ -9856,34 +9860,34 @@
       </c>
       <c r="F163" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>161-w01.jpg</v>
+        <v>160-w01.jpg</v>
       </c>
       <c r="G163" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/161-w01.jpg</v>
+        <v>images/160-w01.jpg</v>
       </c>
       <c r="H163" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/161-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/160-w01.jpg</v>
       </c>
       <c r="I163" s="8"/>
       <c r="J163" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/161-w01.jpg</v>
+        <v>images/160-w01.jpg</v>
       </c>
       <c r="K163" s="8"/>
       <c r="L163" s="8"/>
       <c r="M163" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>161 第1頁</v>
+        <v>160 第1頁</v>
       </c>
       <c r="N163" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-161-w01</v>
+        <v>manifest-160-w01</v>
       </c>
       <c r="O163" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-161-w01</v>
+        <v>canvas-160-w01</v>
       </c>
       <c r="P163" s="8" t="s">
         <v>20</v>
@@ -9893,10 +9897,10 @@
     <row r="164" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>162-w01-p1</v>
+        <v>161-w01-p1</v>
       </c>
       <c r="B164" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>18</v>
@@ -9909,34 +9913,34 @@
       </c>
       <c r="F164" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>162-w01.jpg</v>
+        <v>161-w01.jpg</v>
       </c>
       <c r="G164" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/162-w01.jpg</v>
+        <v>images/161-w01.jpg</v>
       </c>
       <c r="H164" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/162-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/161-w01.jpg</v>
       </c>
       <c r="I164" s="8"/>
       <c r="J164" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/162-w01.jpg</v>
+        <v>images/161-w01.jpg</v>
       </c>
       <c r="K164" s="8"/>
       <c r="L164" s="8"/>
       <c r="M164" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>162 第1頁</v>
+        <v>161 第1頁</v>
       </c>
       <c r="N164" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-162-w01</v>
+        <v>manifest-161-w01</v>
       </c>
       <c r="O164" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-162-w01</v>
+        <v>canvas-161-w01</v>
       </c>
       <c r="P164" s="8" t="s">
         <v>20</v>
@@ -9946,10 +9950,10 @@
     <row r="165" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>163-w01-p1</v>
+        <v>162-w01-p1</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C165" s="8" t="s">
         <v>18</v>
@@ -9962,34 +9966,34 @@
       </c>
       <c r="F165" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>163-w01.jpg</v>
+        <v>162-w01.jpg</v>
       </c>
       <c r="G165" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/163-w01.jpg</v>
+        <v>images/162-w01.jpg</v>
       </c>
       <c r="H165" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/163-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/162-w01.jpg</v>
       </c>
       <c r="I165" s="8"/>
       <c r="J165" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/163-w01.jpg</v>
+        <v>images/162-w01.jpg</v>
       </c>
       <c r="K165" s="8"/>
       <c r="L165" s="8"/>
       <c r="M165" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>163 第1頁</v>
+        <v>162 第1頁</v>
       </c>
       <c r="N165" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-163-w01</v>
+        <v>manifest-162-w01</v>
       </c>
       <c r="O165" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-163-w01</v>
+        <v>canvas-162-w01</v>
       </c>
       <c r="P165" s="8" t="s">
         <v>20</v>
@@ -9999,10 +10003,10 @@
     <row r="166" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>164-w01-p1</v>
+        <v>163-w01-p1</v>
       </c>
       <c r="B166" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>18</v>
@@ -10015,34 +10019,34 @@
       </c>
       <c r="F166" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>164-w01.jpg</v>
+        <v>163-w01.jpg</v>
       </c>
       <c r="G166" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/164-w01.jpg</v>
+        <v>images/163-w01.jpg</v>
       </c>
       <c r="H166" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/164-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/163-w01.jpg</v>
       </c>
       <c r="I166" s="8"/>
       <c r="J166" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/164-w01.jpg</v>
+        <v>images/163-w01.jpg</v>
       </c>
       <c r="K166" s="8"/>
       <c r="L166" s="8"/>
       <c r="M166" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>164 第1頁</v>
+        <v>163 第1頁</v>
       </c>
       <c r="N166" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-164-w01</v>
+        <v>manifest-163-w01</v>
       </c>
       <c r="O166" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-164-w01</v>
+        <v>canvas-163-w01</v>
       </c>
       <c r="P166" s="8" t="s">
         <v>20</v>
@@ -10052,10 +10056,10 @@
     <row r="167" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>165-w01-p1</v>
+        <v>164-w01-p1</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>18</v>
@@ -10068,34 +10072,34 @@
       </c>
       <c r="F167" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>165-w01.jpg</v>
+        <v>164-w01.jpg</v>
       </c>
       <c r="G167" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/165-w01.jpg</v>
+        <v>images/164-w01.jpg</v>
       </c>
       <c r="H167" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/165-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/164-w01.jpg</v>
       </c>
       <c r="I167" s="8"/>
       <c r="J167" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/165-w01.jpg</v>
+        <v>images/164-w01.jpg</v>
       </c>
       <c r="K167" s="8"/>
       <c r="L167" s="8"/>
       <c r="M167" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>165 第1頁</v>
+        <v>164 第1頁</v>
       </c>
       <c r="N167" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-165-w01</v>
+        <v>manifest-164-w01</v>
       </c>
       <c r="O167" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-165-w01</v>
+        <v>canvas-164-w01</v>
       </c>
       <c r="P167" s="8" t="s">
         <v>20</v>
@@ -10105,10 +10109,10 @@
     <row r="168" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>166-w01-p1</v>
+        <v>165-w01-p1</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>18</v>
@@ -10121,34 +10125,34 @@
       </c>
       <c r="F168" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>166-w01.jpg</v>
+        <v>165-w01.jpg</v>
       </c>
       <c r="G168" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/166-w01.jpg</v>
+        <v>images/165-w01.jpg</v>
       </c>
       <c r="H168" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/166-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/165-w01.jpg</v>
       </c>
       <c r="I168" s="8"/>
       <c r="J168" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/166-w01.jpg</v>
+        <v>images/165-w01.jpg</v>
       </c>
       <c r="K168" s="8"/>
       <c r="L168" s="8"/>
       <c r="M168" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>166 第1頁</v>
+        <v>165 第1頁</v>
       </c>
       <c r="N168" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-166-w01</v>
+        <v>manifest-165-w01</v>
       </c>
       <c r="O168" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-166-w01</v>
+        <v>canvas-165-w01</v>
       </c>
       <c r="P168" s="8" t="s">
         <v>20</v>
@@ -10158,10 +10162,10 @@
     <row r="169" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>167-w01-p1</v>
+        <v>166-w01-p1</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>18</v>
@@ -10174,34 +10178,34 @@
       </c>
       <c r="F169" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>167-w01.jpg</v>
+        <v>166-w01.jpg</v>
       </c>
       <c r="G169" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/167-w01.jpg</v>
+        <v>images/166-w01.jpg</v>
       </c>
       <c r="H169" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/167-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/166-w01.jpg</v>
       </c>
       <c r="I169" s="8"/>
       <c r="J169" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/167-w01.jpg</v>
+        <v>images/166-w01.jpg</v>
       </c>
       <c r="K169" s="8"/>
       <c r="L169" s="8"/>
       <c r="M169" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>167 第1頁</v>
+        <v>166 第1頁</v>
       </c>
       <c r="N169" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-167-w01</v>
+        <v>manifest-166-w01</v>
       </c>
       <c r="O169" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-167-w01</v>
+        <v>canvas-166-w01</v>
       </c>
       <c r="P169" s="8" t="s">
         <v>20</v>
@@ -10211,10 +10215,10 @@
     <row r="170" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>168-w01-p1</v>
+        <v>167-w01-p1</v>
       </c>
       <c r="B170" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C170" s="8" t="s">
         <v>18</v>
@@ -10227,34 +10231,34 @@
       </c>
       <c r="F170" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>168-w01.jpg</v>
+        <v>167-w01.jpg</v>
       </c>
       <c r="G170" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/168-w01.jpg</v>
+        <v>images/167-w01.jpg</v>
       </c>
       <c r="H170" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/168-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/167-w01.jpg</v>
       </c>
       <c r="I170" s="8"/>
       <c r="J170" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/168-w01.jpg</v>
+        <v>images/167-w01.jpg</v>
       </c>
       <c r="K170" s="8"/>
       <c r="L170" s="8"/>
       <c r="M170" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>168 第1頁</v>
+        <v>167 第1頁</v>
       </c>
       <c r="N170" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-168-w01</v>
+        <v>manifest-167-w01</v>
       </c>
       <c r="O170" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-168-w01</v>
+        <v>canvas-167-w01</v>
       </c>
       <c r="P170" s="8" t="s">
         <v>20</v>
@@ -10264,10 +10268,10 @@
     <row r="171" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>169-w01-p1</v>
+        <v>168-w01-p1</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>18</v>
@@ -10280,34 +10284,34 @@
       </c>
       <c r="F171" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>169-w01.jpg</v>
+        <v>168-w01.jpg</v>
       </c>
       <c r="G171" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/169-w01.jpg</v>
+        <v>images/168-w01.jpg</v>
       </c>
       <c r="H171" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/169-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/168-w01.jpg</v>
       </c>
       <c r="I171" s="8"/>
       <c r="J171" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/169-w01.jpg</v>
+        <v>images/168-w01.jpg</v>
       </c>
       <c r="K171" s="8"/>
       <c r="L171" s="8"/>
       <c r="M171" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>169 第1頁</v>
+        <v>168 第1頁</v>
       </c>
       <c r="N171" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-169-w01</v>
+        <v>manifest-168-w01</v>
       </c>
       <c r="O171" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-169-w01</v>
+        <v>canvas-168-w01</v>
       </c>
       <c r="P171" s="8" t="s">
         <v>20</v>
@@ -10317,10 +10321,10 @@
     <row r="172" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>170-w01-p1</v>
+        <v>169-w01-p1</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>18</v>
@@ -10333,34 +10337,34 @@
       </c>
       <c r="F172" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>170-w01.jpg</v>
+        <v>169-w01.jpg</v>
       </c>
       <c r="G172" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/170-w01.jpg</v>
+        <v>images/169-w01.jpg</v>
       </c>
       <c r="H172" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/170-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/169-w01.jpg</v>
       </c>
       <c r="I172" s="8"/>
       <c r="J172" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/170-w01.jpg</v>
+        <v>images/169-w01.jpg</v>
       </c>
       <c r="K172" s="8"/>
       <c r="L172" s="8"/>
       <c r="M172" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>170 第1頁</v>
+        <v>169 第1頁</v>
       </c>
       <c r="N172" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-170-w01</v>
+        <v>manifest-169-w01</v>
       </c>
       <c r="O172" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-170-w01</v>
+        <v>canvas-169-w01</v>
       </c>
       <c r="P172" s="8" t="s">
         <v>20</v>
@@ -10370,10 +10374,10 @@
     <row r="173" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>171-w01-p1</v>
+        <v>170-w01-p1</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>18</v>
@@ -10386,34 +10390,34 @@
       </c>
       <c r="F173" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>171-w01.jpg</v>
+        <v>170-w01.jpg</v>
       </c>
       <c r="G173" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/171-w01.jpg</v>
+        <v>images/170-w01.jpg</v>
       </c>
       <c r="H173" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/171-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/170-w01.jpg</v>
       </c>
       <c r="I173" s="8"/>
       <c r="J173" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/171-w01.jpg</v>
+        <v>images/170-w01.jpg</v>
       </c>
       <c r="K173" s="8"/>
       <c r="L173" s="8"/>
       <c r="M173" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>171 第1頁</v>
+        <v>170 第1頁</v>
       </c>
       <c r="N173" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-171-w01</v>
+        <v>manifest-170-w01</v>
       </c>
       <c r="O173" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-171-w01</v>
+        <v>canvas-170-w01</v>
       </c>
       <c r="P173" s="8" t="s">
         <v>20</v>
@@ -10423,10 +10427,10 @@
     <row r="174" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>172-w01-p1</v>
+        <v>171-w01-p1</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>18</v>
@@ -10439,34 +10443,34 @@
       </c>
       <c r="F174" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>172-w01.jpg</v>
+        <v>171-w01.jpg</v>
       </c>
       <c r="G174" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/172-w01.jpg</v>
+        <v>images/171-w01.jpg</v>
       </c>
       <c r="H174" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/172-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/171-w01.jpg</v>
       </c>
       <c r="I174" s="8"/>
       <c r="J174" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/172-w01.jpg</v>
+        <v>images/171-w01.jpg</v>
       </c>
       <c r="K174" s="8"/>
       <c r="L174" s="8"/>
       <c r="M174" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>172 第1頁</v>
+        <v>171 第1頁</v>
       </c>
       <c r="N174" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-172-w01</v>
+        <v>manifest-171-w01</v>
       </c>
       <c r="O174" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-172-w01</v>
+        <v>canvas-171-w01</v>
       </c>
       <c r="P174" s="8" t="s">
         <v>20</v>
@@ -10476,10 +10480,10 @@
     <row r="175" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>173-w01-p1</v>
+        <v>172-w01-p1</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C175" s="8" t="s">
         <v>18</v>
@@ -10492,34 +10496,34 @@
       </c>
       <c r="F175" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>173-w01.jpg</v>
+        <v>172-w01.jpg</v>
       </c>
       <c r="G175" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/173-w01.jpg</v>
+        <v>images/172-w01.jpg</v>
       </c>
       <c r="H175" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/173-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/172-w01.jpg</v>
       </c>
       <c r="I175" s="8"/>
       <c r="J175" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/173-w01.jpg</v>
+        <v>images/172-w01.jpg</v>
       </c>
       <c r="K175" s="8"/>
       <c r="L175" s="8"/>
       <c r="M175" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>173 第1頁</v>
+        <v>172 第1頁</v>
       </c>
       <c r="N175" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-173-w01</v>
+        <v>manifest-172-w01</v>
       </c>
       <c r="O175" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-173-w01</v>
+        <v>canvas-172-w01</v>
       </c>
       <c r="P175" s="8" t="s">
         <v>20</v>
@@ -10529,10 +10533,10 @@
     <row r="176" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>174-w01-p1</v>
+        <v>173-w01-p1</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>18</v>
@@ -10545,34 +10549,34 @@
       </c>
       <c r="F176" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>174-w01.jpg</v>
+        <v>173-w01.jpg</v>
       </c>
       <c r="G176" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/174-w01.jpg</v>
+        <v>images/173-w01.jpg</v>
       </c>
       <c r="H176" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/174-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/173-w01.jpg</v>
       </c>
       <c r="I176" s="8"/>
       <c r="J176" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/174-w01.jpg</v>
+        <v>images/173-w01.jpg</v>
       </c>
       <c r="K176" s="8"/>
       <c r="L176" s="8"/>
       <c r="M176" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>174 第1頁</v>
+        <v>173 第1頁</v>
       </c>
       <c r="N176" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-174-w01</v>
+        <v>manifest-173-w01</v>
       </c>
       <c r="O176" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-174-w01</v>
+        <v>canvas-173-w01</v>
       </c>
       <c r="P176" s="8" t="s">
         <v>20</v>
@@ -10582,10 +10586,10 @@
     <row r="177" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>175-w01-p1</v>
+        <v>174-w01-p1</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>18</v>
@@ -10598,34 +10602,34 @@
       </c>
       <c r="F177" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>175-w01.jpg</v>
+        <v>174-w01.jpg</v>
       </c>
       <c r="G177" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/175-w01.jpg</v>
+        <v>images/174-w01.jpg</v>
       </c>
       <c r="H177" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/175-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/174-w01.jpg</v>
       </c>
       <c r="I177" s="8"/>
       <c r="J177" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/175-w01.jpg</v>
+        <v>images/174-w01.jpg</v>
       </c>
       <c r="K177" s="8"/>
       <c r="L177" s="8"/>
       <c r="M177" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>175 第1頁</v>
+        <v>174 第1頁</v>
       </c>
       <c r="N177" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-175-w01</v>
+        <v>manifest-174-w01</v>
       </c>
       <c r="O177" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-175-w01</v>
+        <v>canvas-174-w01</v>
       </c>
       <c r="P177" s="8" t="s">
         <v>20</v>
@@ -10635,10 +10639,10 @@
     <row r="178" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>176-w01-p1</v>
+        <v>175-w01-p1</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>18</v>
@@ -10651,34 +10655,34 @@
       </c>
       <c r="F178" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>176-w01.jpg</v>
+        <v>175-w01.jpg</v>
       </c>
       <c r="G178" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/176-w01.jpg</v>
+        <v>images/175-w01.jpg</v>
       </c>
       <c r="H178" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/176-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/175-w01.jpg</v>
       </c>
       <c r="I178" s="8"/>
       <c r="J178" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/176-w01.jpg</v>
+        <v>images/175-w01.jpg</v>
       </c>
       <c r="K178" s="8"/>
       <c r="L178" s="8"/>
       <c r="M178" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>176 第1頁</v>
+        <v>175 第1頁</v>
       </c>
       <c r="N178" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-176-w01</v>
+        <v>manifest-175-w01</v>
       </c>
       <c r="O178" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-176-w01</v>
+        <v>canvas-175-w01</v>
       </c>
       <c r="P178" s="8" t="s">
         <v>20</v>
@@ -10688,10 +10692,10 @@
     <row r="179" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>177-w01-p1</v>
+        <v>176-w01-p1</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>18</v>
@@ -10704,34 +10708,34 @@
       </c>
       <c r="F179" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>177-w01.jpg</v>
+        <v>176-w01.jpg</v>
       </c>
       <c r="G179" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/177-w01.jpg</v>
+        <v>images/176-w01.jpg</v>
       </c>
       <c r="H179" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/177-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/176-w01.jpg</v>
       </c>
       <c r="I179" s="8"/>
       <c r="J179" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/177-w01.jpg</v>
+        <v>images/176-w01.jpg</v>
       </c>
       <c r="K179" s="8"/>
       <c r="L179" s="8"/>
       <c r="M179" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>177 第1頁</v>
+        <v>176 第1頁</v>
       </c>
       <c r="N179" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-177-w01</v>
+        <v>manifest-176-w01</v>
       </c>
       <c r="O179" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-177-w01</v>
+        <v>canvas-176-w01</v>
       </c>
       <c r="P179" s="8" t="s">
         <v>20</v>
@@ -10741,10 +10745,10 @@
     <row r="180" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>178-w01-p1</v>
+        <v>177-w01-p1</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>18</v>
@@ -10757,34 +10761,34 @@
       </c>
       <c r="F180" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>178-w01.jpg</v>
+        <v>177-w01.jpg</v>
       </c>
       <c r="G180" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/178-w01.jpg</v>
+        <v>images/177-w01.jpg</v>
       </c>
       <c r="H180" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/178-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/177-w01.jpg</v>
       </c>
       <c r="I180" s="8"/>
       <c r="J180" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/178-w01.jpg</v>
+        <v>images/177-w01.jpg</v>
       </c>
       <c r="K180" s="8"/>
       <c r="L180" s="8"/>
       <c r="M180" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>178 第1頁</v>
+        <v>177 第1頁</v>
       </c>
       <c r="N180" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-178-w01</v>
+        <v>manifest-177-w01</v>
       </c>
       <c r="O180" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-178-w01</v>
+        <v>canvas-177-w01</v>
       </c>
       <c r="P180" s="8" t="s">
         <v>20</v>
@@ -10794,10 +10798,10 @@
     <row r="181" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>179-w01-p1</v>
+        <v>178-w01-p1</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>18</v>
@@ -10810,34 +10814,34 @@
       </c>
       <c r="F181" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>179-w01.jpg</v>
+        <v>178-w01.jpg</v>
       </c>
       <c r="G181" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/179-w01.jpg</v>
+        <v>images/178-w01.jpg</v>
       </c>
       <c r="H181" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/179-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/178-w01.jpg</v>
       </c>
       <c r="I181" s="8"/>
       <c r="J181" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/179-w01.jpg</v>
+        <v>images/178-w01.jpg</v>
       </c>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
       <c r="M181" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>179 第1頁</v>
+        <v>178 第1頁</v>
       </c>
       <c r="N181" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-179-w01</v>
+        <v>manifest-178-w01</v>
       </c>
       <c r="O181" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-179-w01</v>
+        <v>canvas-178-w01</v>
       </c>
       <c r="P181" s="8" t="s">
         <v>20</v>
@@ -10847,10 +10851,10 @@
     <row r="182" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>180-w01-p1</v>
+        <v>179-w01-p1</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>18</v>
@@ -10863,34 +10867,34 @@
       </c>
       <c r="F182" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>180-w01.jpg</v>
+        <v>179-w01.jpg</v>
       </c>
       <c r="G182" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/180-w01.jpg</v>
+        <v>images/179-w01.jpg</v>
       </c>
       <c r="H182" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/180-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/179-w01.jpg</v>
       </c>
       <c r="I182" s="8"/>
       <c r="J182" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/180-w01.jpg</v>
+        <v>images/179-w01.jpg</v>
       </c>
       <c r="K182" s="8"/>
       <c r="L182" s="8"/>
       <c r="M182" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>180 第1頁</v>
+        <v>179 第1頁</v>
       </c>
       <c r="N182" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-180-w01</v>
+        <v>manifest-179-w01</v>
       </c>
       <c r="O182" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-180-w01</v>
+        <v>canvas-179-w01</v>
       </c>
       <c r="P182" s="8" t="s">
         <v>20</v>
@@ -10900,10 +10904,10 @@
     <row r="183" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>181-w01-p1</v>
+        <v>180-w01-p1</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>18</v>
@@ -10916,34 +10920,34 @@
       </c>
       <c r="F183" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>181-w01.jpg</v>
+        <v>180-w01.jpg</v>
       </c>
       <c r="G183" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/181-w01.jpg</v>
+        <v>images/180-w01.jpg</v>
       </c>
       <c r="H183" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/181-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/180-w01.jpg</v>
       </c>
       <c r="I183" s="8"/>
       <c r="J183" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/181-w01.jpg</v>
+        <v>images/180-w01.jpg</v>
       </c>
       <c r="K183" s="8"/>
       <c r="L183" s="8"/>
       <c r="M183" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>181 第1頁</v>
+        <v>180 第1頁</v>
       </c>
       <c r="N183" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-181-w01</v>
+        <v>manifest-180-w01</v>
       </c>
       <c r="O183" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-181-w01</v>
+        <v>canvas-180-w01</v>
       </c>
       <c r="P183" s="8" t="s">
         <v>20</v>
@@ -10953,10 +10957,10 @@
     <row r="184" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>182-w01-p1</v>
+        <v>181-w01-p1</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>18</v>
@@ -10969,34 +10973,34 @@
       </c>
       <c r="F184" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>182-w01.jpg</v>
+        <v>181-w01.jpg</v>
       </c>
       <c r="G184" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/182-w01.jpg</v>
+        <v>images/181-w01.jpg</v>
       </c>
       <c r="H184" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/182-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/181-w01.jpg</v>
       </c>
       <c r="I184" s="8"/>
       <c r="J184" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/182-w01.jpg</v>
+        <v>images/181-w01.jpg</v>
       </c>
       <c r="K184" s="8"/>
       <c r="L184" s="8"/>
       <c r="M184" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>182 第1頁</v>
+        <v>181 第1頁</v>
       </c>
       <c r="N184" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-182-w01</v>
+        <v>manifest-181-w01</v>
       </c>
       <c r="O184" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-182-w01</v>
+        <v>canvas-181-w01</v>
       </c>
       <c r="P184" s="8" t="s">
         <v>20</v>
@@ -11006,10 +11010,10 @@
     <row r="185" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>183-w01-p1</v>
+        <v>182-w01-p1</v>
       </c>
       <c r="B185" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>18</v>
@@ -11022,34 +11026,34 @@
       </c>
       <c r="F185" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>183-w01.jpg</v>
+        <v>182-w01.jpg</v>
       </c>
       <c r="G185" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/183-w01.jpg</v>
+        <v>images/182-w01.jpg</v>
       </c>
       <c r="H185" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/183-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/182-w01.jpg</v>
       </c>
       <c r="I185" s="8"/>
       <c r="J185" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/183-w01.jpg</v>
+        <v>images/182-w01.jpg</v>
       </c>
       <c r="K185" s="8"/>
       <c r="L185" s="8"/>
       <c r="M185" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>183 第1頁</v>
+        <v>182 第1頁</v>
       </c>
       <c r="N185" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-183-w01</v>
+        <v>manifest-182-w01</v>
       </c>
       <c r="O185" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-183-w01</v>
+        <v>canvas-182-w01</v>
       </c>
       <c r="P185" s="8" t="s">
         <v>20</v>
@@ -11059,10 +11063,10 @@
     <row r="186" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>184-w01-p1</v>
+        <v>183-w01-p1</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>18</v>
@@ -11075,34 +11079,34 @@
       </c>
       <c r="F186" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>184-w01.jpg</v>
+        <v>183-w01.jpg</v>
       </c>
       <c r="G186" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/184-w01.jpg</v>
+        <v>images/183-w01.jpg</v>
       </c>
       <c r="H186" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/184-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/183-w01.jpg</v>
       </c>
       <c r="I186" s="8"/>
       <c r="J186" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/184-w01.jpg</v>
+        <v>images/183-w01.jpg</v>
       </c>
       <c r="K186" s="8"/>
       <c r="L186" s="8"/>
       <c r="M186" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>184 第1頁</v>
+        <v>183 第1頁</v>
       </c>
       <c r="N186" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-184-w01</v>
+        <v>manifest-183-w01</v>
       </c>
       <c r="O186" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-184-w01</v>
+        <v>canvas-183-w01</v>
       </c>
       <c r="P186" s="8" t="s">
         <v>20</v>
@@ -11112,10 +11116,10 @@
     <row r="187" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>185-w01-p1</v>
+        <v>184-w01-p1</v>
       </c>
       <c r="B187" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>18</v>
@@ -11128,34 +11132,34 @@
       </c>
       <c r="F187" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>185-w01.jpg</v>
+        <v>184-w01.jpg</v>
       </c>
       <c r="G187" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/185-w01.jpg</v>
+        <v>images/184-w01.jpg</v>
       </c>
       <c r="H187" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/185-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/184-w01.jpg</v>
       </c>
       <c r="I187" s="8"/>
       <c r="J187" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/185-w01.jpg</v>
+        <v>images/184-w01.jpg</v>
       </c>
       <c r="K187" s="8"/>
       <c r="L187" s="8"/>
       <c r="M187" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>185 第1頁</v>
+        <v>184 第1頁</v>
       </c>
       <c r="N187" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-185-w01</v>
+        <v>manifest-184-w01</v>
       </c>
       <c r="O187" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-185-w01</v>
+        <v>canvas-184-w01</v>
       </c>
       <c r="P187" s="8" t="s">
         <v>20</v>
@@ -11165,10 +11169,10 @@
     <row r="188" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>186-w01-p1</v>
+        <v>185-w01-p1</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>18</v>
@@ -11181,34 +11185,34 @@
       </c>
       <c r="F188" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>186-w01.jpg</v>
+        <v>185-w01.jpg</v>
       </c>
       <c r="G188" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/186-w01.jpg</v>
+        <v>images/185-w01.jpg</v>
       </c>
       <c r="H188" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/186-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/185-w01.jpg</v>
       </c>
       <c r="I188" s="8"/>
       <c r="J188" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/186-w01.jpg</v>
+        <v>images/185-w01.jpg</v>
       </c>
       <c r="K188" s="8"/>
       <c r="L188" s="8"/>
       <c r="M188" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>186 第1頁</v>
+        <v>185 第1頁</v>
       </c>
       <c r="N188" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-186-w01</v>
+        <v>manifest-185-w01</v>
       </c>
       <c r="O188" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-186-w01</v>
+        <v>canvas-185-w01</v>
       </c>
       <c r="P188" s="8" t="s">
         <v>20</v>
@@ -11218,10 +11222,10 @@
     <row r="189" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>187-w01-p1</v>
+        <v>186-w01-p1</v>
       </c>
       <c r="B189" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>18</v>
@@ -11234,34 +11238,34 @@
       </c>
       <c r="F189" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>187-w01.jpg</v>
+        <v>186-w01.jpg</v>
       </c>
       <c r="G189" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/187-w01.jpg</v>
+        <v>images/186-w01.jpg</v>
       </c>
       <c r="H189" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/187-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/186-w01.jpg</v>
       </c>
       <c r="I189" s="8"/>
       <c r="J189" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/187-w01.jpg</v>
+        <v>images/186-w01.jpg</v>
       </c>
       <c r="K189" s="8"/>
       <c r="L189" s="8"/>
       <c r="M189" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>187 第1頁</v>
+        <v>186 第1頁</v>
       </c>
       <c r="N189" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-187-w01</v>
+        <v>manifest-186-w01</v>
       </c>
       <c r="O189" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-187-w01</v>
+        <v>canvas-186-w01</v>
       </c>
       <c r="P189" s="8" t="s">
         <v>20</v>
@@ -11271,10 +11275,10 @@
     <row r="190" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>188-w01-p1</v>
+        <v>187-w01-p1</v>
       </c>
       <c r="B190" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>18</v>
@@ -11287,34 +11291,34 @@
       </c>
       <c r="F190" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>188-w01.jpg</v>
+        <v>187-w01.jpg</v>
       </c>
       <c r="G190" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/188-w01.jpg</v>
+        <v>images/187-w01.jpg</v>
       </c>
       <c r="H190" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/188-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/187-w01.jpg</v>
       </c>
       <c r="I190" s="8"/>
       <c r="J190" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/188-w01.jpg</v>
+        <v>images/187-w01.jpg</v>
       </c>
       <c r="K190" s="8"/>
       <c r="L190" s="8"/>
       <c r="M190" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>188 第1頁</v>
+        <v>187 第1頁</v>
       </c>
       <c r="N190" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-188-w01</v>
+        <v>manifest-187-w01</v>
       </c>
       <c r="O190" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-188-w01</v>
+        <v>canvas-187-w01</v>
       </c>
       <c r="P190" s="8" t="s">
         <v>20</v>
@@ -11324,10 +11328,10 @@
     <row r="191" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>189-w01-p1</v>
+        <v>188-w01-p1</v>
       </c>
       <c r="B191" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>18</v>
@@ -11340,34 +11344,34 @@
       </c>
       <c r="F191" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>189-w01.jpg</v>
+        <v>188-w01.jpg</v>
       </c>
       <c r="G191" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/189-w01.jpg</v>
+        <v>images/188-w01.jpg</v>
       </c>
       <c r="H191" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/189-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/188-w01.jpg</v>
       </c>
       <c r="I191" s="8"/>
       <c r="J191" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/189-w01.jpg</v>
+        <v>images/188-w01.jpg</v>
       </c>
       <c r="K191" s="8"/>
       <c r="L191" s="8"/>
       <c r="M191" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>189 第1頁</v>
+        <v>188 第1頁</v>
       </c>
       <c r="N191" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-189-w01</v>
+        <v>manifest-188-w01</v>
       </c>
       <c r="O191" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-189-w01</v>
+        <v>canvas-188-w01</v>
       </c>
       <c r="P191" s="8" t="s">
         <v>20</v>
@@ -11377,10 +11381,10 @@
     <row r="192" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>190-w01-p1</v>
+        <v>189-w01-p1</v>
       </c>
       <c r="B192" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>18</v>
@@ -11393,34 +11397,34 @@
       </c>
       <c r="F192" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>190-w01.jpg</v>
+        <v>189-w01.jpg</v>
       </c>
       <c r="G192" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/190-w01.jpg</v>
+        <v>images/189-w01.jpg</v>
       </c>
       <c r="H192" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/190-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/189-w01.jpg</v>
       </c>
       <c r="I192" s="8"/>
       <c r="J192" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/190-w01.jpg</v>
+        <v>images/189-w01.jpg</v>
       </c>
       <c r="K192" s="8"/>
       <c r="L192" s="8"/>
       <c r="M192" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>190 第1頁</v>
+        <v>189 第1頁</v>
       </c>
       <c r="N192" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-190-w01</v>
+        <v>manifest-189-w01</v>
       </c>
       <c r="O192" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-190-w01</v>
+        <v>canvas-189-w01</v>
       </c>
       <c r="P192" s="8" t="s">
         <v>20</v>
@@ -11430,10 +11434,10 @@
     <row r="193" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="7" t="str">
         <f t="shared" si="16"/>
-        <v>191-w01-p1</v>
+        <v>190-w01-p1</v>
       </c>
       <c r="B193" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>18</v>
@@ -11446,34 +11450,34 @@
       </c>
       <c r="F193" s="8" t="str">
         <f t="shared" si="17"/>
-        <v>191-w01.jpg</v>
+        <v>190-w01.jpg</v>
       </c>
       <c r="G193" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>images/191-w01.jpg</v>
+        <v>images/190-w01.jpg</v>
       </c>
       <c r="H193" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/191-w01.jpg</v>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/190-w01.jpg</v>
       </c>
       <c r="I193" s="8"/>
       <c r="J193" s="8" t="str">
         <f t="shared" si="20"/>
-        <v>images/191-w01.jpg</v>
+        <v>images/190-w01.jpg</v>
       </c>
       <c r="K193" s="8"/>
       <c r="L193" s="8"/>
       <c r="M193" s="7" t="str">
         <f t="shared" si="21"/>
-        <v>191 第1頁</v>
+        <v>190 第1頁</v>
       </c>
       <c r="N193" s="7" t="str">
         <f t="shared" si="22"/>
-        <v>manifest-191-w01</v>
+        <v>manifest-190-w01</v>
       </c>
       <c r="O193" s="7" t="str">
         <f t="shared" si="23"/>
-        <v>canvas-191-w01</v>
+        <v>canvas-190-w01</v>
       </c>
       <c r="P193" s="8" t="s">
         <v>20</v>
@@ -11482,11 +11486,11 @@
     </row>
     <row r="194" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="7" t="str">
-        <f t="shared" ref="A194:A248" si="24">IF(OR(B194="",D194=""),"",B194&amp;IF(C194="","","-"&amp;C194)&amp;"-p"&amp;D194)</f>
-        <v>192-w01-p1</v>
+        <f t="shared" si="16"/>
+        <v>191-w01-p1</v>
       </c>
       <c r="B194" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>18</v>
@@ -11498,35 +11502,35 @@
         <v>19</v>
       </c>
       <c r="F194" s="8" t="str">
-        <f t="shared" ref="F194:F248" si="25">IF(OR(B194="",C194=""),"",B194&amp;"-"&amp;C194&amp;".jpg")</f>
-        <v>192-w01.jpg</v>
+        <f t="shared" si="17"/>
+        <v>191-w01.jpg</v>
       </c>
       <c r="G194" s="8" t="str">
-        <f t="shared" ref="G194:G248" si="26">IF(OR(B194="",C194=""),"","images/"&amp;B194&amp;"-"&amp;C194&amp;".jpg")</f>
-        <v>images/192-w01.jpg</v>
+        <f t="shared" si="18"/>
+        <v>images/191-w01.jpg</v>
       </c>
       <c r="H194" s="8" t="str">
-        <f t="shared" ref="H194:H248" si="27">IF(OR(B194="",C194=""),"","https://scholarbo.github.io/soseki-manuscripts/images/"&amp;B194&amp;"-"&amp;C194&amp;".jpg")</f>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/192-w01.jpg</v>
+        <f t="shared" si="19"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/191-w01.jpg</v>
       </c>
       <c r="I194" s="8"/>
       <c r="J194" s="8" t="str">
-        <f t="shared" ref="J194:J248" si="28">IF(OR(B194="",C194="",E194&lt;&gt;"iiif"),"","images/"&amp;B194&amp;"-"&amp;C194&amp;".jpg")</f>
-        <v>images/192-w01.jpg</v>
+        <f t="shared" si="20"/>
+        <v>images/191-w01.jpg</v>
       </c>
       <c r="K194" s="8"/>
       <c r="L194" s="8"/>
       <c r="M194" s="7" t="str">
-        <f t="shared" ref="M194:M248" si="29">IF(OR(B194="",D194=""),"",B194&amp;IF(C194="","",IF(C194="w01",""," 第"&amp;VALUE(RIGHT(C194,2))&amp;"版"))&amp;" 第"&amp;D194&amp;"頁")</f>
-        <v>192 第1頁</v>
+        <f t="shared" si="21"/>
+        <v>191 第1頁</v>
       </c>
       <c r="N194" s="7" t="str">
-        <f t="shared" ref="N194:N248" si="30">IF(OR(B194="",C194=""),"","manifest-"&amp;B194&amp;"-"&amp;C194)</f>
-        <v>manifest-192-w01</v>
+        <f t="shared" si="22"/>
+        <v>manifest-191-w01</v>
       </c>
       <c r="O194" s="7" t="str">
-        <f t="shared" ref="O194:O248" si="31">IF(OR(B194="",C194="",D194=""),"","canvas-"&amp;B194&amp;"-"&amp;C194&amp;IF(D194=1,"","-p"&amp;D194))</f>
-        <v>canvas-192-w01</v>
+        <f t="shared" si="23"/>
+        <v>canvas-191-w01</v>
       </c>
       <c r="P194" s="8" t="s">
         <v>20</v>
@@ -11535,11 +11539,11 @@
     </row>
     <row r="195" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>193-w01-p1</v>
+        <f t="shared" ref="A195:A249" si="32">IF(OR(B195="",D195=""),"",B195&amp;IF(C195="","","-"&amp;C195)&amp;"-p"&amp;D195)</f>
+        <v>192-w01-p1</v>
       </c>
       <c r="B195" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C195" s="8" t="s">
         <v>18</v>
@@ -11551,35 +11555,35 @@
         <v>19</v>
       </c>
       <c r="F195" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>193-w01.jpg</v>
+        <f t="shared" ref="F195:F249" si="33">IF(OR(B195="",C195=""),"",B195&amp;"-"&amp;C195&amp;".jpg")</f>
+        <v>192-w01.jpg</v>
       </c>
       <c r="G195" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/193-w01.jpg</v>
+        <f t="shared" ref="G195:G249" si="34">IF(OR(B195="",C195=""),"","images/"&amp;B195&amp;"-"&amp;C195&amp;".jpg")</f>
+        <v>images/192-w01.jpg</v>
       </c>
       <c r="H195" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/193-w01.jpg</v>
+        <f t="shared" ref="H195:H249" si="35">IF(OR(B195="",C195=""),"","https://scholarbo.github.io/soseki-manuscripts/images/"&amp;B195&amp;"-"&amp;C195&amp;".jpg")</f>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/192-w01.jpg</v>
       </c>
       <c r="I195" s="8"/>
       <c r="J195" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/193-w01.jpg</v>
+        <f t="shared" ref="J195:J249" si="36">IF(OR(B195="",C195="",E195&lt;&gt;"iiif"),"","images/"&amp;B195&amp;"-"&amp;C195&amp;".jpg")</f>
+        <v>images/192-w01.jpg</v>
       </c>
       <c r="K195" s="8"/>
       <c r="L195" s="8"/>
       <c r="M195" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>193 第1頁</v>
+        <f t="shared" ref="M195:M249" si="37">IF(OR(B195="",D195=""),"",B195&amp;IF(C195="","",IF(C195="w01",""," 第"&amp;VALUE(RIGHT(C195,2))&amp;"版"))&amp;" 第"&amp;D195&amp;"頁")</f>
+        <v>192 第1頁</v>
       </c>
       <c r="N195" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-193-w01</v>
+        <f t="shared" ref="N195:N249" si="38">IF(OR(B195="",C195=""),"","manifest-"&amp;B195&amp;"-"&amp;C195)</f>
+        <v>manifest-192-w01</v>
       </c>
       <c r="O195" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-193-w01</v>
+        <f t="shared" ref="O195:O249" si="39">IF(OR(B195="",C195="",D195=""),"","canvas-"&amp;B195&amp;"-"&amp;C195&amp;IF(D195=1,"","-p"&amp;D195))</f>
+        <v>canvas-192-w01</v>
       </c>
       <c r="P195" s="8" t="s">
         <v>20</v>
@@ -11588,11 +11592,11 @@
     </row>
     <row r="196" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>194-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>193-w01-p1</v>
       </c>
       <c r="B196" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C196" s="8" t="s">
         <v>18</v>
@@ -11604,35 +11608,35 @@
         <v>19</v>
       </c>
       <c r="F196" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>194-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>193-w01.jpg</v>
       </c>
       <c r="G196" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/194-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/193-w01.jpg</v>
       </c>
       <c r="H196" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/194-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/193-w01.jpg</v>
       </c>
       <c r="I196" s="8"/>
       <c r="J196" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/194-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/193-w01.jpg</v>
       </c>
       <c r="K196" s="8"/>
       <c r="L196" s="8"/>
       <c r="M196" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>194 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>193 第1頁</v>
       </c>
       <c r="N196" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-194-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-193-w01</v>
       </c>
       <c r="O196" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-194-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-193-w01</v>
       </c>
       <c r="P196" s="8" t="s">
         <v>20</v>
@@ -11641,11 +11645,11 @@
     </row>
     <row r="197" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>195-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>194-w01-p1</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C197" s="8" t="s">
         <v>18</v>
@@ -11657,35 +11661,35 @@
         <v>19</v>
       </c>
       <c r="F197" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>195-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>194-w01.jpg</v>
       </c>
       <c r="G197" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/195-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/194-w01.jpg</v>
       </c>
       <c r="H197" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/195-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/194-w01.jpg</v>
       </c>
       <c r="I197" s="8"/>
       <c r="J197" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/195-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/194-w01.jpg</v>
       </c>
       <c r="K197" s="8"/>
       <c r="L197" s="8"/>
       <c r="M197" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>195 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>194 第1頁</v>
       </c>
       <c r="N197" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-195-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-194-w01</v>
       </c>
       <c r="O197" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-195-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-194-w01</v>
       </c>
       <c r="P197" s="8" t="s">
         <v>20</v>
@@ -11694,11 +11698,11 @@
     </row>
     <row r="198" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>196-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>195-w01-p1</v>
       </c>
       <c r="B198" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C198" s="8" t="s">
         <v>18</v>
@@ -11710,35 +11714,35 @@
         <v>19</v>
       </c>
       <c r="F198" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>196-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>195-w01.jpg</v>
       </c>
       <c r="G198" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/196-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/195-w01.jpg</v>
       </c>
       <c r="H198" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/196-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/195-w01.jpg</v>
       </c>
       <c r="I198" s="8"/>
       <c r="J198" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/196-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/195-w01.jpg</v>
       </c>
       <c r="K198" s="8"/>
       <c r="L198" s="8"/>
       <c r="M198" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>196 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>195 第1頁</v>
       </c>
       <c r="N198" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-196-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-195-w01</v>
       </c>
       <c r="O198" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-196-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-195-w01</v>
       </c>
       <c r="P198" s="8" t="s">
         <v>20</v>
@@ -11747,11 +11751,11 @@
     </row>
     <row r="199" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>197-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>196-w01-p1</v>
       </c>
       <c r="B199" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C199" s="8" t="s">
         <v>18</v>
@@ -11763,35 +11767,35 @@
         <v>19</v>
       </c>
       <c r="F199" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>197-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>196-w01.jpg</v>
       </c>
       <c r="G199" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/197-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/196-w01.jpg</v>
       </c>
       <c r="H199" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/197-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/196-w01.jpg</v>
       </c>
       <c r="I199" s="8"/>
       <c r="J199" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/197-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/196-w01.jpg</v>
       </c>
       <c r="K199" s="8"/>
       <c r="L199" s="8"/>
       <c r="M199" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>197 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>196 第1頁</v>
       </c>
       <c r="N199" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-197-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-196-w01</v>
       </c>
       <c r="O199" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-197-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-196-w01</v>
       </c>
       <c r="P199" s="8" t="s">
         <v>20</v>
@@ -11800,11 +11804,11 @@
     </row>
     <row r="200" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>198-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>197-w01-p1</v>
       </c>
       <c r="B200" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C200" s="8" t="s">
         <v>18</v>
@@ -11816,35 +11820,35 @@
         <v>19</v>
       </c>
       <c r="F200" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>198-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>197-w01.jpg</v>
       </c>
       <c r="G200" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/198-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/197-w01.jpg</v>
       </c>
       <c r="H200" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/198-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/197-w01.jpg</v>
       </c>
       <c r="I200" s="8"/>
       <c r="J200" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/198-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/197-w01.jpg</v>
       </c>
       <c r="K200" s="8"/>
       <c r="L200" s="8"/>
       <c r="M200" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>198 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>197 第1頁</v>
       </c>
       <c r="N200" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-198-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-197-w01</v>
       </c>
       <c r="O200" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-198-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-197-w01</v>
       </c>
       <c r="P200" s="8" t="s">
         <v>20</v>
@@ -11853,11 +11857,11 @@
     </row>
     <row r="201" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>199-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>198-w01-p1</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>18</v>
@@ -11869,35 +11873,35 @@
         <v>19</v>
       </c>
       <c r="F201" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>199-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>198-w01.jpg</v>
       </c>
       <c r="G201" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/199-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/198-w01.jpg</v>
       </c>
       <c r="H201" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/199-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/198-w01.jpg</v>
       </c>
       <c r="I201" s="8"/>
       <c r="J201" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/199-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/198-w01.jpg</v>
       </c>
       <c r="K201" s="8"/>
       <c r="L201" s="8"/>
       <c r="M201" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>199 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>198 第1頁</v>
       </c>
       <c r="N201" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-199-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-198-w01</v>
       </c>
       <c r="O201" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-199-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-198-w01</v>
       </c>
       <c r="P201" s="8" t="s">
         <v>20</v>
@@ -11906,11 +11910,11 @@
     </row>
     <row r="202" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>200-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>199-w01-p1</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C202" s="8" t="s">
         <v>18</v>
@@ -11922,35 +11926,35 @@
         <v>19</v>
       </c>
       <c r="F202" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>200-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>199-w01.jpg</v>
       </c>
       <c r="G202" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/200-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/199-w01.jpg</v>
       </c>
       <c r="H202" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/200-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/199-w01.jpg</v>
       </c>
       <c r="I202" s="8"/>
       <c r="J202" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/200-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/199-w01.jpg</v>
       </c>
       <c r="K202" s="8"/>
       <c r="L202" s="8"/>
       <c r="M202" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>200 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>199 第1頁</v>
       </c>
       <c r="N202" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-200-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-199-w01</v>
       </c>
       <c r="O202" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-200-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-199-w01</v>
       </c>
       <c r="P202" s="8" t="s">
         <v>20</v>
@@ -11959,11 +11963,11 @@
     </row>
     <row r="203" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>201-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>200-w01-p1</v>
       </c>
       <c r="B203" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C203" s="8" t="s">
         <v>18</v>
@@ -11975,35 +11979,35 @@
         <v>19</v>
       </c>
       <c r="F203" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>201-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>200-w01.jpg</v>
       </c>
       <c r="G203" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/201-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/200-w01.jpg</v>
       </c>
       <c r="H203" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/201-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/200-w01.jpg</v>
       </c>
       <c r="I203" s="8"/>
       <c r="J203" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/201-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/200-w01.jpg</v>
       </c>
       <c r="K203" s="8"/>
       <c r="L203" s="8"/>
       <c r="M203" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>201 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>200 第1頁</v>
       </c>
       <c r="N203" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-201-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-200-w01</v>
       </c>
       <c r="O203" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-201-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-200-w01</v>
       </c>
       <c r="P203" s="8" t="s">
         <v>20</v>
@@ -12012,11 +12016,11 @@
     </row>
     <row r="204" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>202-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>201-w01-p1</v>
       </c>
       <c r="B204" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C204" s="8" t="s">
         <v>18</v>
@@ -12028,35 +12032,35 @@
         <v>19</v>
       </c>
       <c r="F204" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>202-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>201-w01.jpg</v>
       </c>
       <c r="G204" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/202-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/201-w01.jpg</v>
       </c>
       <c r="H204" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/202-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/201-w01.jpg</v>
       </c>
       <c r="I204" s="8"/>
       <c r="J204" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/202-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/201-w01.jpg</v>
       </c>
       <c r="K204" s="8"/>
       <c r="L204" s="8"/>
       <c r="M204" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>202 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>201 第1頁</v>
       </c>
       <c r="N204" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-202-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-201-w01</v>
       </c>
       <c r="O204" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-202-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-201-w01</v>
       </c>
       <c r="P204" s="8" t="s">
         <v>20</v>
@@ -12065,11 +12069,11 @@
     </row>
     <row r="205" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>203-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>202-w01-p1</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C205" s="8" t="s">
         <v>18</v>
@@ -12081,48 +12085,48 @@
         <v>19</v>
       </c>
       <c r="F205" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>203-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>202-w01.jpg</v>
       </c>
       <c r="G205" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/203-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/202-w01.jpg</v>
       </c>
       <c r="H205" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/203-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/202-w01.jpg</v>
       </c>
       <c r="I205" s="8"/>
       <c r="J205" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/203-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/202-w01.jpg</v>
       </c>
       <c r="K205" s="8"/>
       <c r="L205" s="8"/>
       <c r="M205" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>203 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>202 第1頁</v>
       </c>
       <c r="N205" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-203-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-202-w01</v>
       </c>
       <c r="O205" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-203-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-202-w01</v>
       </c>
       <c r="P205" s="8" t="s">
         <v>20</v>
       </c>
       <c r="Q205" s="8"/>
     </row>
-    <row r="206" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>204-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>203-w01-p1</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C206" s="8" t="s">
         <v>18</v>
@@ -12134,48 +12138,48 @@
         <v>19</v>
       </c>
       <c r="F206" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>204-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>203-w01.jpg</v>
       </c>
       <c r="G206" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/204-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/203-w01.jpg</v>
       </c>
       <c r="H206" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/204-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/203-w01.jpg</v>
       </c>
       <c r="I206" s="8"/>
       <c r="J206" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/204-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/203-w01.jpg</v>
       </c>
       <c r="K206" s="8"/>
       <c r="L206" s="8"/>
       <c r="M206" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>204 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>203 第1頁</v>
       </c>
       <c r="N206" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-204-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-203-w01</v>
       </c>
       <c r="O206" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-204-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-203-w01</v>
       </c>
       <c r="P206" s="8" t="s">
         <v>20</v>
       </c>
       <c r="Q206" s="8"/>
     </row>
-    <row r="207" spans="1:17" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:17" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>205-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>204-w01-p1</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C207" s="8" t="s">
         <v>18</v>
@@ -12187,48 +12191,48 @@
         <v>19</v>
       </c>
       <c r="F207" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>205-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>204-w01.jpg</v>
       </c>
       <c r="G207" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/205-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/204-w01.jpg</v>
       </c>
       <c r="H207" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/205-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/204-w01.jpg</v>
       </c>
       <c r="I207" s="8"/>
       <c r="J207" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/205-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/204-w01.jpg</v>
       </c>
       <c r="K207" s="8"/>
       <c r="L207" s="8"/>
       <c r="M207" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>205 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>204 第1頁</v>
       </c>
       <c r="N207" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-205-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-204-w01</v>
       </c>
       <c r="O207" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-205-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-204-w01</v>
       </c>
       <c r="P207" s="8" t="s">
         <v>20</v>
       </c>
       <c r="Q207" s="8"/>
     </row>
-    <row r="208" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:17" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>206-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>205-w01-p1</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C208" s="8" t="s">
         <v>18</v>
@@ -12240,35 +12244,35 @@
         <v>19</v>
       </c>
       <c r="F208" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>206-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>205-w01.jpg</v>
       </c>
       <c r="G208" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/206-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/205-w01.jpg</v>
       </c>
       <c r="H208" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/206-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/205-w01.jpg</v>
       </c>
       <c r="I208" s="8"/>
       <c r="J208" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/206-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/205-w01.jpg</v>
       </c>
       <c r="K208" s="8"/>
       <c r="L208" s="8"/>
       <c r="M208" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>206 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>205 第1頁</v>
       </c>
       <c r="N208" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-206-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-205-w01</v>
       </c>
       <c r="O208" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-206-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-205-w01</v>
       </c>
       <c r="P208" s="8" t="s">
         <v>20</v>
@@ -12277,11 +12281,11 @@
     </row>
     <row r="209" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>207-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>206-w01-p1</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C209" s="8" t="s">
         <v>18</v>
@@ -12293,35 +12297,35 @@
         <v>19</v>
       </c>
       <c r="F209" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>207-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>206-w01.jpg</v>
       </c>
       <c r="G209" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/207-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/206-w01.jpg</v>
       </c>
       <c r="H209" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/207-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/206-w01.jpg</v>
       </c>
       <c r="I209" s="8"/>
       <c r="J209" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/207-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/206-w01.jpg</v>
       </c>
       <c r="K209" s="8"/>
       <c r="L209" s="8"/>
       <c r="M209" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>207 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>206 第1頁</v>
       </c>
       <c r="N209" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-207-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-206-w01</v>
       </c>
       <c r="O209" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-207-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-206-w01</v>
       </c>
       <c r="P209" s="8" t="s">
         <v>20</v>
@@ -12330,11 +12334,11 @@
     </row>
     <row r="210" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>208-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>207-w01-p1</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C210" s="8" t="s">
         <v>18</v>
@@ -12346,48 +12350,48 @@
         <v>19</v>
       </c>
       <c r="F210" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>208-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>207-w01.jpg</v>
       </c>
       <c r="G210" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/208-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/207-w01.jpg</v>
       </c>
       <c r="H210" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/208-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/207-w01.jpg</v>
       </c>
       <c r="I210" s="8"/>
       <c r="J210" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v>images/208-w01.jpg</v>
+        <f t="shared" si="36"/>
+        <v>images/207-w01.jpg</v>
       </c>
       <c r="K210" s="8"/>
       <c r="L210" s="8"/>
       <c r="M210" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>208 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>207 第1頁</v>
       </c>
       <c r="N210" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-208-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-207-w01</v>
       </c>
       <c r="O210" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-208-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-207-w01</v>
       </c>
       <c r="P210" s="8" t="s">
         <v>20</v>
       </c>
       <c r="Q210" s="8"/>
     </row>
-    <row r="211" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:17" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>209-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>208-w01-p1</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C211" s="8" t="s">
         <v>18</v>
@@ -12396,51 +12400,51 @@
         <v>1</v>
       </c>
       <c r="E211" s="8" t="s">
-        <v>230</v>
+        <v>19</v>
       </c>
       <c r="F211" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>209-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>208-w01.jpg</v>
       </c>
       <c r="G211" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/209-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/208-w01.jpg</v>
       </c>
       <c r="H211" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/209-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/208-w01.jpg</v>
       </c>
       <c r="I211" s="8"/>
       <c r="J211" s="8" t="str">
-        <f t="shared" si="28"/>
-        <v/>
+        <f t="shared" si="36"/>
+        <v>images/208-w01.jpg</v>
       </c>
       <c r="K211" s="8"/>
       <c r="L211" s="8"/>
       <c r="M211" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>209 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>208 第1頁</v>
       </c>
       <c r="N211" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-209-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-208-w01</v>
       </c>
       <c r="O211" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-209-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-208-w01</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="Q211" s="8"/>
     </row>
     <row r="212" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>210-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>209-w01-p1</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C212" s="8" t="s">
         <v>18</v>
@@ -12452,35 +12456,35 @@
         <v>230</v>
       </c>
       <c r="F212" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>210-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>209-w01.jpg</v>
       </c>
       <c r="G212" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/210-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/209-w01.jpg</v>
       </c>
       <c r="H212" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/210-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/209-w01.jpg</v>
       </c>
       <c r="I212" s="8"/>
       <c r="J212" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K212" s="8"/>
       <c r="L212" s="8"/>
       <c r="M212" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>210 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>209 第1頁</v>
       </c>
       <c r="N212" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-210-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-209-w01</v>
       </c>
       <c r="O212" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-210-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-209-w01</v>
       </c>
       <c r="P212" s="8" t="s">
         <v>231</v>
@@ -12489,11 +12493,11 @@
     </row>
     <row r="213" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>211-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>210-w01-p1</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C213" s="8" t="s">
         <v>18</v>
@@ -12505,35 +12509,35 @@
         <v>230</v>
       </c>
       <c r="F213" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>211-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>210-w01.jpg</v>
       </c>
       <c r="G213" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/211-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/210-w01.jpg</v>
       </c>
       <c r="H213" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/211-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/210-w01.jpg</v>
       </c>
       <c r="I213" s="8"/>
       <c r="J213" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K213" s="8"/>
       <c r="L213" s="8"/>
       <c r="M213" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>211 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>210 第1頁</v>
       </c>
       <c r="N213" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-211-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-210-w01</v>
       </c>
       <c r="O213" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-211-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-210-w01</v>
       </c>
       <c r="P213" s="8" t="s">
         <v>231</v>
@@ -12542,11 +12546,11 @@
     </row>
     <row r="214" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>212-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>211-w01-p1</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C214" s="8" t="s">
         <v>18</v>
@@ -12558,35 +12562,35 @@
         <v>230</v>
       </c>
       <c r="F214" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>212-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>211-w01.jpg</v>
       </c>
       <c r="G214" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/212-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/211-w01.jpg</v>
       </c>
       <c r="H214" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/212-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/211-w01.jpg</v>
       </c>
       <c r="I214" s="8"/>
       <c r="J214" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K214" s="8"/>
       <c r="L214" s="8"/>
       <c r="M214" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>212 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>211 第1頁</v>
       </c>
       <c r="N214" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-212-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-211-w01</v>
       </c>
       <c r="O214" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-212-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-211-w01</v>
       </c>
       <c r="P214" s="8" t="s">
         <v>231</v>
@@ -12595,11 +12599,11 @@
     </row>
     <row r="215" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>213-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>212-w01-p1</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C215" s="8" t="s">
         <v>18</v>
@@ -12611,35 +12615,35 @@
         <v>230</v>
       </c>
       <c r="F215" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>213-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>212-w01.jpg</v>
       </c>
       <c r="G215" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/213-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/212-w01.jpg</v>
       </c>
       <c r="H215" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/213-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/212-w01.jpg</v>
       </c>
       <c r="I215" s="8"/>
       <c r="J215" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K215" s="8"/>
       <c r="L215" s="8"/>
       <c r="M215" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>213 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>212 第1頁</v>
       </c>
       <c r="N215" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-213-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-212-w01</v>
       </c>
       <c r="O215" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-213-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-212-w01</v>
       </c>
       <c r="P215" s="8" t="s">
         <v>231</v>
@@ -12648,11 +12652,11 @@
     </row>
     <row r="216" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>214-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>213-w01-p1</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C216" s="8" t="s">
         <v>18</v>
@@ -12664,35 +12668,35 @@
         <v>230</v>
       </c>
       <c r="F216" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>214-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>213-w01.jpg</v>
       </c>
       <c r="G216" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/214-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/213-w01.jpg</v>
       </c>
       <c r="H216" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/214-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/213-w01.jpg</v>
       </c>
       <c r="I216" s="8"/>
       <c r="J216" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K216" s="8"/>
       <c r="L216" s="8"/>
       <c r="M216" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>214 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>213 第1頁</v>
       </c>
       <c r="N216" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-214-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-213-w01</v>
       </c>
       <c r="O216" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-214-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-213-w01</v>
       </c>
       <c r="P216" s="8" t="s">
         <v>231</v>
@@ -12701,11 +12705,11 @@
     </row>
     <row r="217" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>215-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>214-w01-p1</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C217" s="8" t="s">
         <v>18</v>
@@ -12717,35 +12721,35 @@
         <v>230</v>
       </c>
       <c r="F217" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>215-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>214-w01.jpg</v>
       </c>
       <c r="G217" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/215-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/214-w01.jpg</v>
       </c>
       <c r="H217" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/215-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/214-w01.jpg</v>
       </c>
       <c r="I217" s="8"/>
       <c r="J217" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K217" s="8"/>
       <c r="L217" s="8"/>
       <c r="M217" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>215 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>214 第1頁</v>
       </c>
       <c r="N217" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-215-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-214-w01</v>
       </c>
       <c r="O217" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-215-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-214-w01</v>
       </c>
       <c r="P217" s="8" t="s">
         <v>231</v>
@@ -12754,11 +12758,11 @@
     </row>
     <row r="218" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v>216-w01-p1</v>
+        <f t="shared" si="32"/>
+        <v>215-w01-p1</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C218" s="8" t="s">
         <v>18</v>
@@ -12770,35 +12774,35 @@
         <v>230</v>
       </c>
       <c r="F218" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v>216-w01.jpg</v>
+        <f t="shared" si="33"/>
+        <v>215-w01.jpg</v>
       </c>
       <c r="G218" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v>images/216-w01.jpg</v>
+        <f t="shared" si="34"/>
+        <v>images/215-w01.jpg</v>
       </c>
       <c r="H218" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v>https://scholarbo.github.io/soseki-manuscripts/images/216-w01.jpg</v>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/215-w01.jpg</v>
       </c>
       <c r="I218" s="8"/>
       <c r="J218" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K218" s="8"/>
       <c r="L218" s="8"/>
       <c r="M218" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v>216 第1頁</v>
+        <f t="shared" si="37"/>
+        <v>215 第1頁</v>
       </c>
       <c r="N218" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v>manifest-216-w01</v>
+        <f t="shared" si="38"/>
+        <v>manifest-215-w01</v>
       </c>
       <c r="O218" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v>canvas-216-w01</v>
+        <f t="shared" si="39"/>
+        <v>canvas-215-w01</v>
       </c>
       <c r="P218" s="8" t="s">
         <v>231</v>
@@ -12807,50 +12811,60 @@
     </row>
     <row r="219" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="7" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
-      <c r="D219" s="8"/>
-      <c r="E219" s="8"/>
+        <f t="shared" si="32"/>
+        <v>216-w01-p1</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C219" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D219" s="8">
+        <v>1</v>
+      </c>
+      <c r="E219" s="8" t="s">
+        <v>230</v>
+      </c>
       <c r="F219" s="8" t="str">
-        <f t="shared" si="25"/>
-        <v/>
+        <f t="shared" si="33"/>
+        <v>216-w01.jpg</v>
       </c>
       <c r="G219" s="8" t="str">
-        <f t="shared" si="26"/>
-        <v/>
+        <f t="shared" si="34"/>
+        <v>images/216-w01.jpg</v>
       </c>
       <c r="H219" s="8" t="str">
-        <f t="shared" si="27"/>
-        <v/>
+        <f t="shared" si="35"/>
+        <v>https://scholarbo.github.io/soseki-manuscripts/images/216-w01.jpg</v>
       </c>
       <c r="I219" s="8"/>
       <c r="J219" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K219" s="8"/>
       <c r="L219" s="8"/>
       <c r="M219" s="7" t="str">
-        <f t="shared" si="29"/>
-        <v/>
+        <f t="shared" si="37"/>
+        <v>216 第1頁</v>
       </c>
       <c r="N219" s="7" t="str">
-        <f t="shared" si="30"/>
-        <v/>
+        <f t="shared" si="38"/>
+        <v>manifest-216-w01</v>
       </c>
       <c r="O219" s="7" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="P219" s="8"/>
+        <f t="shared" si="39"/>
+        <v>canvas-216-w01</v>
+      </c>
+      <c r="P219" s="8" t="s">
+        <v>231</v>
+      </c>
       <c r="Q219" s="8"/>
     </row>
     <row r="220" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B220" s="8"/>
@@ -12858,34 +12872,34 @@
       <c r="D220" s="8"/>
       <c r="E220" s="8"/>
       <c r="F220" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G220" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H220" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I220" s="8"/>
       <c r="J220" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K220" s="8"/>
       <c r="L220" s="8"/>
       <c r="M220" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N220" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O220" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P220" s="8"/>
@@ -12893,7 +12907,7 @@
     </row>
     <row r="221" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B221" s="8"/>
@@ -12901,34 +12915,34 @@
       <c r="D221" s="8"/>
       <c r="E221" s="8"/>
       <c r="F221" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G221" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H221" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I221" s="8"/>
       <c r="J221" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K221" s="8"/>
       <c r="L221" s="8"/>
       <c r="M221" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N221" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O221" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P221" s="8"/>
@@ -12936,7 +12950,7 @@
     </row>
     <row r="222" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B222" s="8"/>
@@ -12944,34 +12958,34 @@
       <c r="D222" s="8"/>
       <c r="E222" s="8"/>
       <c r="F222" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G222" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H222" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I222" s="8"/>
       <c r="J222" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K222" s="8"/>
       <c r="L222" s="8"/>
       <c r="M222" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N222" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O222" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P222" s="8"/>
@@ -12979,7 +12993,7 @@
     </row>
     <row r="223" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B223" s="8"/>
@@ -12987,34 +13001,34 @@
       <c r="D223" s="8"/>
       <c r="E223" s="8"/>
       <c r="F223" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G223" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H223" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I223" s="8"/>
       <c r="J223" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K223" s="8"/>
       <c r="L223" s="8"/>
       <c r="M223" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N223" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O223" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P223" s="8"/>
@@ -13022,7 +13036,7 @@
     </row>
     <row r="224" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B224" s="8"/>
@@ -13030,34 +13044,34 @@
       <c r="D224" s="8"/>
       <c r="E224" s="8"/>
       <c r="F224" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G224" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H224" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I224" s="8"/>
       <c r="J224" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K224" s="8"/>
       <c r="L224" s="8"/>
       <c r="M224" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N224" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O224" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P224" s="8"/>
@@ -13065,7 +13079,7 @@
     </row>
     <row r="225" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B225" s="8"/>
@@ -13073,34 +13087,34 @@
       <c r="D225" s="8"/>
       <c r="E225" s="8"/>
       <c r="F225" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G225" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H225" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I225" s="8"/>
       <c r="J225" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K225" s="8"/>
       <c r="L225" s="8"/>
       <c r="M225" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N225" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O225" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P225" s="8"/>
@@ -13108,7 +13122,7 @@
     </row>
     <row r="226" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B226" s="8"/>
@@ -13116,34 +13130,34 @@
       <c r="D226" s="8"/>
       <c r="E226" s="8"/>
       <c r="F226" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G226" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H226" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I226" s="8"/>
       <c r="J226" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K226" s="8"/>
       <c r="L226" s="8"/>
       <c r="M226" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N226" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O226" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P226" s="8"/>
@@ -13151,7 +13165,7 @@
     </row>
     <row r="227" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B227" s="8"/>
@@ -13159,34 +13173,34 @@
       <c r="D227" s="8"/>
       <c r="E227" s="8"/>
       <c r="F227" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G227" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H227" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I227" s="8"/>
       <c r="J227" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K227" s="8"/>
       <c r="L227" s="8"/>
       <c r="M227" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N227" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O227" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P227" s="8"/>
@@ -13194,7 +13208,7 @@
     </row>
     <row r="228" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B228" s="8"/>
@@ -13202,34 +13216,34 @@
       <c r="D228" s="8"/>
       <c r="E228" s="8"/>
       <c r="F228" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G228" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H228" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I228" s="8"/>
       <c r="J228" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K228" s="8"/>
       <c r="L228" s="8"/>
       <c r="M228" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N228" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O228" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P228" s="8"/>
@@ -13237,7 +13251,7 @@
     </row>
     <row r="229" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B229" s="8"/>
@@ -13245,34 +13259,34 @@
       <c r="D229" s="8"/>
       <c r="E229" s="8"/>
       <c r="F229" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G229" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H229" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I229" s="8"/>
       <c r="J229" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K229" s="8"/>
       <c r="L229" s="8"/>
       <c r="M229" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N229" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O229" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P229" s="8"/>
@@ -13280,7 +13294,7 @@
     </row>
     <row r="230" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B230" s="8"/>
@@ -13288,34 +13302,34 @@
       <c r="D230" s="8"/>
       <c r="E230" s="8"/>
       <c r="F230" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G230" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H230" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I230" s="8"/>
       <c r="J230" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K230" s="8"/>
       <c r="L230" s="8"/>
       <c r="M230" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N230" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O230" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P230" s="8"/>
@@ -13323,7 +13337,7 @@
     </row>
     <row r="231" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B231" s="8"/>
@@ -13331,34 +13345,34 @@
       <c r="D231" s="8"/>
       <c r="E231" s="8"/>
       <c r="F231" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G231" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H231" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I231" s="8"/>
       <c r="J231" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K231" s="8"/>
       <c r="L231" s="8"/>
       <c r="M231" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N231" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O231" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P231" s="8"/>
@@ -13366,7 +13380,7 @@
     </row>
     <row r="232" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B232" s="8"/>
@@ -13374,34 +13388,34 @@
       <c r="D232" s="8"/>
       <c r="E232" s="8"/>
       <c r="F232" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G232" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H232" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I232" s="8"/>
       <c r="J232" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K232" s="8"/>
       <c r="L232" s="8"/>
       <c r="M232" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N232" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O232" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P232" s="8"/>
@@ -13409,7 +13423,7 @@
     </row>
     <row r="233" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B233" s="8"/>
@@ -13417,34 +13431,34 @@
       <c r="D233" s="8"/>
       <c r="E233" s="8"/>
       <c r="F233" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G233" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H233" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I233" s="8"/>
       <c r="J233" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K233" s="8"/>
       <c r="L233" s="8"/>
       <c r="M233" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N233" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O233" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P233" s="8"/>
@@ -13452,7 +13466,7 @@
     </row>
     <row r="234" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B234" s="8"/>
@@ -13460,34 +13474,34 @@
       <c r="D234" s="8"/>
       <c r="E234" s="8"/>
       <c r="F234" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G234" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H234" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I234" s="8"/>
       <c r="J234" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K234" s="8"/>
       <c r="L234" s="8"/>
       <c r="M234" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N234" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O234" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P234" s="8"/>
@@ -13495,7 +13509,7 @@
     </row>
     <row r="235" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B235" s="8"/>
@@ -13503,34 +13517,34 @@
       <c r="D235" s="8"/>
       <c r="E235" s="8"/>
       <c r="F235" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G235" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H235" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I235" s="8"/>
       <c r="J235" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K235" s="8"/>
       <c r="L235" s="8"/>
       <c r="M235" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N235" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O235" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P235" s="8"/>
@@ -13538,7 +13552,7 @@
     </row>
     <row r="236" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B236" s="8"/>
@@ -13546,34 +13560,34 @@
       <c r="D236" s="8"/>
       <c r="E236" s="8"/>
       <c r="F236" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G236" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H236" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I236" s="8"/>
       <c r="J236" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K236" s="8"/>
       <c r="L236" s="8"/>
       <c r="M236" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N236" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O236" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P236" s="8"/>
@@ -13581,7 +13595,7 @@
     </row>
     <row r="237" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B237" s="8"/>
@@ -13589,34 +13603,34 @@
       <c r="D237" s="8"/>
       <c r="E237" s="8"/>
       <c r="F237" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G237" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H237" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I237" s="8"/>
       <c r="J237" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K237" s="8"/>
       <c r="L237" s="8"/>
       <c r="M237" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N237" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O237" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P237" s="8"/>
@@ -13624,7 +13638,7 @@
     </row>
     <row r="238" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B238" s="8"/>
@@ -13632,34 +13646,34 @@
       <c r="D238" s="8"/>
       <c r="E238" s="8"/>
       <c r="F238" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G238" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H238" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I238" s="8"/>
       <c r="J238" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K238" s="8"/>
       <c r="L238" s="8"/>
       <c r="M238" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N238" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O238" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P238" s="8"/>
@@ -13667,7 +13681,7 @@
     </row>
     <row r="239" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B239" s="8"/>
@@ -13675,34 +13689,34 @@
       <c r="D239" s="8"/>
       <c r="E239" s="8"/>
       <c r="F239" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G239" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H239" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I239" s="8"/>
       <c r="J239" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K239" s="8"/>
       <c r="L239" s="8"/>
       <c r="M239" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N239" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O239" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P239" s="8"/>
@@ -13710,7 +13724,7 @@
     </row>
     <row r="240" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B240" s="8"/>
@@ -13718,34 +13732,34 @@
       <c r="D240" s="8"/>
       <c r="E240" s="8"/>
       <c r="F240" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G240" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H240" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I240" s="8"/>
       <c r="J240" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K240" s="8"/>
       <c r="L240" s="8"/>
       <c r="M240" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N240" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O240" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P240" s="8"/>
@@ -13753,7 +13767,7 @@
     </row>
     <row r="241" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B241" s="8"/>
@@ -13761,34 +13775,34 @@
       <c r="D241" s="8"/>
       <c r="E241" s="8"/>
       <c r="F241" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G241" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H241" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I241" s="8"/>
       <c r="J241" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K241" s="8"/>
       <c r="L241" s="8"/>
       <c r="M241" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N241" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O241" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P241" s="8"/>
@@ -13796,7 +13810,7 @@
     </row>
     <row r="242" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B242" s="8"/>
@@ -13804,34 +13818,34 @@
       <c r="D242" s="8"/>
       <c r="E242" s="8"/>
       <c r="F242" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G242" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H242" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I242" s="8"/>
       <c r="J242" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K242" s="8"/>
       <c r="L242" s="8"/>
       <c r="M242" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N242" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O242" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P242" s="8"/>
@@ -13839,7 +13853,7 @@
     </row>
     <row r="243" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B243" s="8"/>
@@ -13847,34 +13861,34 @@
       <c r="D243" s="8"/>
       <c r="E243" s="8"/>
       <c r="F243" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G243" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H243" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I243" s="8"/>
       <c r="J243" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K243" s="8"/>
       <c r="L243" s="8"/>
       <c r="M243" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N243" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O243" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P243" s="8"/>
@@ -13882,7 +13896,7 @@
     </row>
     <row r="244" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B244" s="8"/>
@@ -13890,34 +13904,34 @@
       <c r="D244" s="8"/>
       <c r="E244" s="8"/>
       <c r="F244" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G244" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H244" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I244" s="8"/>
       <c r="J244" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K244" s="8"/>
       <c r="L244" s="8"/>
       <c r="M244" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N244" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O244" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P244" s="8"/>
@@ -13925,7 +13939,7 @@
     </row>
     <row r="245" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B245" s="8"/>
@@ -13933,34 +13947,34 @@
       <c r="D245" s="8"/>
       <c r="E245" s="8"/>
       <c r="F245" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G245" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H245" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I245" s="8"/>
       <c r="J245" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K245" s="8"/>
       <c r="L245" s="8"/>
       <c r="M245" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N245" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O245" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P245" s="8"/>
@@ -13968,7 +13982,7 @@
     </row>
     <row r="246" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B246" s="8"/>
@@ -13976,34 +13990,34 @@
       <c r="D246" s="8"/>
       <c r="E246" s="8"/>
       <c r="F246" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G246" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H246" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I246" s="8"/>
       <c r="J246" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K246" s="8"/>
       <c r="L246" s="8"/>
       <c r="M246" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N246" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O246" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P246" s="8"/>
@@ -14011,7 +14025,7 @@
     </row>
     <row r="247" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B247" s="8"/>
@@ -14019,34 +14033,34 @@
       <c r="D247" s="8"/>
       <c r="E247" s="8"/>
       <c r="F247" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G247" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H247" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I247" s="8"/>
       <c r="J247" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K247" s="8"/>
       <c r="L247" s="8"/>
       <c r="M247" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N247" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O247" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P247" s="8"/>
@@ -14054,7 +14068,7 @@
     </row>
     <row r="248" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="7" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="B248" s="8"/>
@@ -14062,46 +14076,89 @@
       <c r="D248" s="8"/>
       <c r="E248" s="8"/>
       <c r="F248" s="8" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G248" s="8" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="H248" s="8" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="I248" s="8"/>
       <c r="J248" s="8" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="K248" s="8"/>
       <c r="L248" s="8"/>
       <c r="M248" s="7" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N248" s="7" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O248" s="7" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P248" s="8"/>
       <c r="Q248" s="8"/>
+    </row>
+    <row r="249" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A249" s="7" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="B249" s="8"/>
+      <c r="C249" s="8"/>
+      <c r="D249" s="8"/>
+      <c r="E249" s="8"/>
+      <c r="F249" s="8" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="G249" s="8" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="H249" s="8" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="I249" s="8"/>
+      <c r="J249" s="8" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="K249" s="8"/>
+      <c r="L249" s="8"/>
+      <c r="M249" s="7" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="N249" s="7" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="O249" s="7" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="P249" s="8"/>
+      <c r="Q249" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="E2:E248" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="E2:E249" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>image_roles</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="P2:P248" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="P2:P249" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>status_list</formula1>
     </dataValidation>
   </dataValidations>
